--- a/docs/assets/cases/profile.xlsx
+++ b/docs/assets/cases/profile.xlsx
@@ -232,7 +232,7 @@
     <t>"MarsProfileReport"</t>
   </si>
   <si>
-    <t>"f9800620-f9c9-4190-9620-733700d525fb"</t>
+    <t>"5919494c-bf16-4986-8949-0ff69b105153"</t>
   </si>
   <si>
     <t>1</t>
@@ -253,7 +253,7 @@
     <t>{"table":"calculation_status","diagnostics":"parameters.diagnostics/fit_failures/raw_ks_diagnostics","scope":"feature/target/group/metric; profile status contains exceptional outcomes only, not all trend cells"}</t>
   </si>
   <si>
-    <t>{"mars_version":"0.0.28","polars_version":"1.42.0","generated_at_utc":"2026-10-02T13:06:49.040584+00:00","input_type":"polars","row_count":18000,"column_count":17,"features":["main_score","aux_score","income","channel","sparse","aux_probability"],"metrics":["missing","zeros","mean","psi"],"group_col":"dataset","time_col":null,"time_grain":null,"benchmark_row_count":6000,"categorical_features":["channel"],"profile_config":{"missing_values":[],"special_values":[-999],"overview_batch_size":500,"psi_batch_size":50,"psi_remove_empty_bins":true,"psi_merge_small_bins":true,"psi_min_bin_size":0.02,"psi_cv_ignore_threshold":0.05,"enable_sparkline":false,"sparkline_sample_size":200000,"sparkline_bins":8,"psi_n_bins":10,"psi_bin_method":"quantile","psi_include_missing":false,"psi_include_special":false},"diagnostics":[{"component":"psi","features":["sparse"],"reason":"Degenerate feature: single unique value."}]}</t>
+    <t>{"mars_version":"0.0.28","polars_version":"1.44.2","generated_at_utc":"2026-10-02T16:48:31.191592+00:00","input_type":"polars","row_count":18000,"column_count":18,"features":["main_score","aux_score","income","channel","sparse","aux_probability"],"metrics":["missing","zeros","mean","psi"],"group_col":"dataset","time_col":null,"time_grain":null,"benchmark_row_count":6000,"categorical_features":["channel"],"profile_config":{"missing_values":[],"special_values":[-999],"overview_batch_size":500,"psi_batch_size":50,"psi_remove_empty_bins":true,"psi_merge_small_bins":true,"psi_min_bin_size":0.02,"psi_cv_ignore_threshold":0.05,"enable_sparkline":false,"sparkline_sample_size":200000,"sparkline_bins":8,"psi_n_bins":10,"psi_bin_method":"quantile","psi_include_missing":false,"psi_include_special":false},"diagnostics":[{"component":"psi","features":["sparse"],"reason":"Degenerate feature: single unique value."}]}</t>
   </si>
   <si>
     <t>["只组织已有统计，未计算表不在目录中；失败和跳过见 parameters.diagnostics / fit_failures。","Null 不是数值 0；风险指标需结合标签表现状态，样本分布使用全样本。","比较前核对样本范围、权重、缺失/特殊箱、拟合来源、排序口径及参考来源；关联不代表因果。"]</t>
@@ -352,7 +352,7 @@
     <t>['channel']</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>[{'component': 'psi', 'features': ['sparse'], 'reason': 'Degenerate feature: single unique value.'}]</t>
@@ -361,7 +361,7 @@
     <t>['main_score', 'aux_score', 'income', 'channel', 'sparse', 'aux_probability']</t>
   </si>
   <si>
-    <t>2026-10-02T13:06:49.040584+00:00</t>
+    <t>2026-10-02T16:48:31.191592+00:00</t>
   </si>
   <si>
     <t>dataset</t>
@@ -376,7 +376,7 @@
     <t>['missing', 'zeros', 'mean', 'psi']</t>
   </si>
   <si>
-    <t>1.42.0</t>
+    <t>1.44.2</t>
   </si>
   <si>
     <t>{'missing_values': [], 'special_values': [-999], 'overview_batch_size': 500, 'psi_batch_size': 50, 'psi_remove_empty_bins': True, 'psi_merge_small_bins': True, 'psi_min_bin_size': 0.02, 'psi_cv_ignore_threshold': 0.05, 'enable_sparkline': False, 'sparkline_sample_size': 200000, 'sparkline_bins': 8, 'psi_n_bins': 10, 'psi_bin_method': 'quantile', 'psi_include_missing': False, 'psi_include_special': False}</t>
@@ -959,8 +959,7 @@
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1029,7 +1028,7 @@
         <v>0.4384754118743955</v>
       </c>
       <c r="G3" s="9">
-        <v>0.3392095469859594</v>
+        <v>0.3392095469859593</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1046,13 +1045,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="10">
-        <v>0.004357630751802145</v>
+        <v>0.004357630751802146</v>
       </c>
       <c r="F4" s="4">
         <v>0.003370800672785611</v>
       </c>
       <c r="G4" s="2">
-        <v>0.001436833477341213</v>
+        <v>0.001436833477341212</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1075,7 +1074,7 @@
         <v>0.001203001154266639</v>
       </c>
       <c r="G5" s="2">
-        <v>0.0006336696959507832</v>
+        <v>0.0006336696959507833</v>
       </c>
     </row>
     <row r="6" spans="1:7">

--- a/docs/assets/cases/profile.xlsx
+++ b/docs/assets/cases/profile.xlsx
@@ -1120,7 +1120,7 @@
     <t>"MarsProfileReport"</t>
   </si>
   <si>
-    <t>"5d00f397-1768-44b0-9306-cd2531e7e9a6"</t>
+    <t>"39fae55f-e3a7-4d88-86b2-edcdb1d533dd"</t>
   </si>
   <si>
     <t>1</t>
@@ -1141,7 +1141,7 @@
     <t>{"table":"calculation_status","diagnostics":"parameters.diagnostics/fit_failures/raw_ks_diagnostics","scope":"feature/target/group/metric; profile status contains exceptional outcomes only, not all trend cells"}</t>
   </si>
   <si>
-    <t>{"mars_version":"0.0.28","polars_version":"1.42.0","generated_at_utc":"2026-10-15T14:46:46.380326+00:00","input_type":"polars","row_count":356255,"column_count":124,"features":["NAME_CONTRACT_TYPE","CODE_GENDER","FLAG_OWN_CAR","FLAG_OWN_REALTY","CNT_CHILDREN","AMT_INCOME_TOTAL","AMT_ANNUITY","AMT_GOODS_PRICE","NAME_TYPE_SUITE","NAME_INCOME_TYPE","NAME_EDUCATION_TYPE","NAME_FAMILY_STATUS","NAME_HOUSING_TYPE","REGION_POPULATION_RELATIVE","DAYS_BIRTH","DAYS_EMPLOYED","DAYS_REGISTRATION","DAYS_ID_PUBLISH","OWN_CAR_AGE","FLAG_MOBIL","FLAG_EMP_PHONE","FLAG_WORK_PHONE","FLAG_CONT_MOBILE","FLAG_PHONE","FLAG_EMAIL","OCCUPATION_TYPE","CNT_FAM_MEMBERS","REGION_RATING_CLIENT","REGION_RATING_CLIENT_W_CITY","WEEKDAY_APPR_PROCESS_START","HOUR_APPR_PROCESS_START","REG_REGION_NOT_LIVE_REGION","REG_REGION_NOT_WORK_REGION","LIVE_REGION_NOT_WORK_REGION","REG_CITY_NOT_LIVE_CITY","REG_CITY_NOT_WORK_CITY","LIVE_CITY_NOT_WORK_CITY","ORGANIZATION_TYPE","EXT_SOURCE_1","EXT_SOURCE_2","EXT_SOURCE_3","APARTMENTS_AVG","BASEMENTAREA_AVG","YEARS_BEGINEXPLUATATION_AVG","YEARS_BUILD_AVG","COMMONAREA_AVG","ELEVATORS_AVG","ENTRANCES_AVG","FLOORSMAX_AVG","FLOORSMIN_AVG","LANDAREA_AVG","LIVINGAPARTMENTS_AVG","LIVINGAREA_AVG","NONLIVINGAPARTMENTS_AVG","NONLIVINGAREA_AVG","APARTMENTS_MODE","BASEMENTAREA_MODE","YEARS_BEGINEXPLUATATION_MODE","YEARS_BUILD_MODE","COMMONAREA_MODE","ELEVATORS_MODE","ENTRANCES_MODE","FLOORSMAX_MODE","FLOORSMIN_MODE","LANDAREA_MODE","LIVINGAPARTMENTS_MODE","LIVINGAREA_MODE","NONLIVINGAPARTMENTS_MODE","NONLIVINGAREA_MODE","APARTMENTS_MEDI","BASEMENTAREA_MEDI","YEARS_BEGINEXPLUATATION_MEDI","YEARS_BUILD_MEDI","COMMONAREA_MEDI","ELEVATORS_MEDI","ENTRANCES_MEDI","FLOORSMAX_MEDI","FLOORSMIN_MEDI","LANDAREA_MEDI","LIVINGAPARTMENTS_MEDI","LIVINGAREA_MEDI","NONLIVINGAPARTMENTS_MEDI","NONLIVINGAREA_MEDI","FONDKAPREMONT_MODE","HOUSETYPE_MODE","TOTALAREA_MODE","WALLSMATERIAL_MODE","EMERGENCYSTATE_MODE","OBS_30_CNT_SOCIAL_CIRCLE","DEF_30_CNT_SOCIAL_CIRCLE","OBS_60_CNT_SOCIAL_CIRCLE","DEF_60_CNT_SOCIAL_CIRCLE","DAYS_LAST_PHONE_CHANGE","FLAG_DOCUMENT_2","FLAG_DOCUMENT_3","FLAG_DOCUMENT_4","FLAG_DOCUMENT_5","FLAG_DOCUMENT_6","FLAG_DOCUMENT_7","FLAG_DOCUMENT_8","FLAG_DOCUMENT_9","FLAG_DOCUMENT_10","FLAG_DOCUMENT_11","FLAG_DOCUMENT_12","FLAG_DOCUMENT_13","FLAG_DOCUMENT_14","FLAG_DOCUMENT_15","FLAG_DOCUMENT_16","FLAG_DOCUMENT_17","FLAG_DOCUMENT_18","FLAG_DOCUMENT_19","FLAG_DOCUMENT_20","FLAG_DOCUMENT_21","AMT_REQ_CREDIT_BUREAU_HOUR","AMT_REQ_CREDIT_BUREAU_DAY","AMT_REQ_CREDIT_BUREAU_WEEK","AMT_REQ_CREDIT_BUREAU_MON","AMT_REQ_CREDIT_BUREAU_QRT","AMT_REQ_CREDIT_BUREAU_YEAR"],"feature_dtypes":{"NAME_CONTRACT_TYPE":"String","CODE_GENDER":"String","FLAG_OWN_CAR":"String","FLAG_OWN_REALTY":"String","CNT_CHILDREN":"Int64","AMT_INCOME_TOTAL":"Float64","AMT_ANNUITY":"Float64","AMT_GOODS_PRICE":"Float64","NAME_TYPE_SUITE":"String","NAME_INCOME_TYPE":"String","NAME_EDUCATION_TYPE":"String","NAME_FAMILY_STATUS":"String","NAME_HOUSING_TYPE":"String","REGION_POPULATION_RELATIVE":"Float64","DAYS_BIRTH":"Int64","DAYS_EMPLOYED":"Int64","DAYS_REGISTRATION":"Float64","DAYS_ID_PUBLISH":"Int64","OWN_CAR_AGE":"Float64","FLAG_MOBIL":"Int64","FLAG_EMP_PHONE":"Int64","FLAG_WORK_PHONE":"Int64","FLAG_CONT_MOBILE":"Int64","FLAG_PHONE":"Int64","FLAG_EMAIL":"Int64","OCCUPATION_TYPE":"String","CNT_FAM_MEMBERS":"Float64","REGION_RATING_CLIENT":"Int64","REGION_RATING_CLIENT_W_CITY":"Int64","WEEKDAY_APPR_PROCESS_START":"String","HOUR_APPR_PROCESS_START":"Int64","REG_REGION_NOT_LIVE_REGION":"Int64","REG_REGION_NOT_WORK_REGION":"Int64","LIVE_REGION_NOT_WORK_REGION":"Int64","REG_CITY_NOT_LIVE_CITY":"Int64","REG_CITY_NOT_WORK_CITY":"Int64","LIVE_CITY_NOT_WORK_CITY":"Int64","ORGANIZATION_TYPE":"String","EXT_SOURCE_1":"Float64","EXT_SOURCE_2":"Float64","EXT_SOURCE_3":"Float64","APARTMENTS_AVG":"Float64","BASEMENTAREA_AVG":"Float64","YEARS_BEGINEXPLUATATION_AVG":"Float64","YEARS_BUILD_AVG":"Float64","COMMONAREA_AVG":"Float64","ELEVATORS_AVG":"Float64","ENTRANCES_AVG":"Float64","FLOORSMAX_AVG":"Float64","FLOORSMIN_AVG":"Float64","LANDAREA_AVG":"Float64","LIVINGAPARTMENTS_AVG":"Float64","LIVINGAREA_AVG":"Float64","NONLIVINGAPARTMENTS_AVG":"Float64","NONLIVINGAREA_AVG":"Float64","APARTMENTS_MODE":"Float64","BASEMENTAREA_MODE":"Float64","YEARS_BEGINEXPLUATATION_MODE":"Float64","YEARS_BUILD_MODE":"Float64","COMMONAREA_MODE":"Float64","ELEVATORS_MODE":"Float64","ENTRANCES_MODE":"Float64","FLOORSMAX_MODE":"Float64","FLOORSMIN_MODE":"Float64","LANDAREA_MODE":"Float64","LIVINGAPARTMENTS_MODE":"Float64","LIVINGAREA_MODE":"Float64","NONLIVINGAPARTMENTS_MODE":"Float64","NONLIVINGAREA_MODE":"Float64","APARTMENTS_MEDI":"Float64","BASEMENTAREA_MEDI":"Float64","YEARS_BEGINEXPLUATATION_MEDI":"Float64","YEARS_BUILD_MEDI":"Float64","COMMONAREA_MEDI":"Float64","ELEVATORS_MEDI":"Float64","ENTRANCES_MEDI":"Float64","FLOORSMAX_MEDI":"Float64","FLOORSMIN_MEDI":"Float64","LANDAREA_MEDI":"Float64","LIVINGAPARTMENTS_MEDI":"Float64","LIVINGAREA_MEDI":"Float64","NONLIVINGAPARTMENTS_MEDI":"Float64","NONLIVINGAREA_MEDI":"Float64","FONDKAPREMONT_MODE":"String","HOUSETYPE_MODE":"String","TOTALAREA_MODE":"Float64","WALLSMATERIAL_MODE":"String","EMERGENCYSTATE_MODE":"String","OBS_30_CNT_SOCIAL_CIRCLE":"Float64","DEF_30_CNT_SOCIAL_CIRCLE":"Float64","OBS_60_CNT_SOCIAL_CIRCLE":"Float64","DEF_60_CNT_SOCIAL_CIRCLE":"Float64","DAYS_LAST_PHONE_CHANGE":"Float64","FLAG_DOCUMENT_2":"Int64","FLAG_DOCUMENT_3":"Int64","FLAG_DOCUMENT_4":"Int64","FLAG_DOCUMENT_5":"Int64","FLAG_DOCUMENT_6":"Int64","FLAG_DOCUMENT_7":"Int64","FLAG_DOCUMENT_8":"Int64","FLAG_DOCUMENT_9":"Int64","FLAG_DOCUMENT_10":"Int64","FLAG_DOCUMENT_11":"Int64","FLAG_DOCUMENT_12":"Int64","FLAG_DOCUMENT_13":"Int64","FLAG_DOCUMENT_14":"Int64","FLAG_DOCUMENT_15":"Int64","FLAG_DOCUMENT_16":"Int64","FLAG_DOCUMENT_17":"Int64","FLAG_DOCUMENT_18":"Int64","FLAG_DOCUMENT_19":"Int64","FLAG_DOCUMENT_20":"Int64","FLAG_DOCUMENT_21":"Int64","AMT_REQ_CREDIT_BUREAU_HOUR":"Float64","AMT_REQ_CREDIT_BUREAU_DAY":"Float64","AMT_REQ_CREDIT_BUREAU_WEEK":"Float64","AMT_REQ_CREDIT_BUREAU_MON":"Float64","AMT_REQ_CREDIT_BUREAU_QRT":"Float64","AMT_REQ_CREDIT_BUREAU_YEAR":"Float64"},"metrics":["missing","zeros","mean","psi"],"group_col":"dataset_flag","time_col":null,"time_grain":null,"benchmark_row_count":215374,"categorical_features":["NAME_CONTRACT_TYPE","CODE_GENDER","FLAG_OWN_CAR","FLAG_OWN_REALTY","NAME_TYPE_SUITE","NAME_INCOME_TYPE","NAME_EDUCATION_TYPE","NAME_FAMILY_STATUS","NAME_HOUSING_TYPE","OCCUPATION_TYPE","WEEKDAY_APPR_PROCESS_START","ORGANIZATION_TYPE","FONDKAPREMONT_MODE","HOUSETYPE_MODE","WALLSMATERIAL_MODE","EMERGENCYSTATE_MODE"],"profile_config":{"missing_values":[],"special_values":[],"overview_batch_size":500,"psi_batch_size":50,"psi_remove_empty_bins":true,"psi_merge_small_bins":true,"psi_min_bin_size":0.02,"psi_cv_ignore_threshold":0.05,"enable_sparkline":false,"sparkline_sample_size":200000,"sparkline_bins":8,"psi_n_bins":10,"psi_bin_method":"quantile","psi_include_missing":false,"psi_include_special":false},"diagnostics":[]}</t>
+    <t>{"mars_version":"0.0.28","polars_version":"1.42.0","generated_at_utc":"2026-10-22T15:04:08.748771+00:00","input_type":"polars","row_count":356255,"column_count":124,"features":["NAME_CONTRACT_TYPE","CODE_GENDER","FLAG_OWN_CAR","FLAG_OWN_REALTY","CNT_CHILDREN","AMT_INCOME_TOTAL","AMT_ANNUITY","AMT_GOODS_PRICE","NAME_TYPE_SUITE","NAME_INCOME_TYPE","NAME_EDUCATION_TYPE","NAME_FAMILY_STATUS","NAME_HOUSING_TYPE","REGION_POPULATION_RELATIVE","DAYS_BIRTH","DAYS_EMPLOYED","DAYS_REGISTRATION","DAYS_ID_PUBLISH","OWN_CAR_AGE","FLAG_MOBIL","FLAG_EMP_PHONE","FLAG_WORK_PHONE","FLAG_CONT_MOBILE","FLAG_PHONE","FLAG_EMAIL","OCCUPATION_TYPE","CNT_FAM_MEMBERS","REGION_RATING_CLIENT","REGION_RATING_CLIENT_W_CITY","WEEKDAY_APPR_PROCESS_START","HOUR_APPR_PROCESS_START","REG_REGION_NOT_LIVE_REGION","REG_REGION_NOT_WORK_REGION","LIVE_REGION_NOT_WORK_REGION","REG_CITY_NOT_LIVE_CITY","REG_CITY_NOT_WORK_CITY","LIVE_CITY_NOT_WORK_CITY","ORGANIZATION_TYPE","EXT_SOURCE_1","EXT_SOURCE_2","EXT_SOURCE_3","APARTMENTS_AVG","BASEMENTAREA_AVG","YEARS_BEGINEXPLUATATION_AVG","YEARS_BUILD_AVG","COMMONAREA_AVG","ELEVATORS_AVG","ENTRANCES_AVG","FLOORSMAX_AVG","FLOORSMIN_AVG","LANDAREA_AVG","LIVINGAPARTMENTS_AVG","LIVINGAREA_AVG","NONLIVINGAPARTMENTS_AVG","NONLIVINGAREA_AVG","APARTMENTS_MODE","BASEMENTAREA_MODE","YEARS_BEGINEXPLUATATION_MODE","YEARS_BUILD_MODE","COMMONAREA_MODE","ELEVATORS_MODE","ENTRANCES_MODE","FLOORSMAX_MODE","FLOORSMIN_MODE","LANDAREA_MODE","LIVINGAPARTMENTS_MODE","LIVINGAREA_MODE","NONLIVINGAPARTMENTS_MODE","NONLIVINGAREA_MODE","APARTMENTS_MEDI","BASEMENTAREA_MEDI","YEARS_BEGINEXPLUATATION_MEDI","YEARS_BUILD_MEDI","COMMONAREA_MEDI","ELEVATORS_MEDI","ENTRANCES_MEDI","FLOORSMAX_MEDI","FLOORSMIN_MEDI","LANDAREA_MEDI","LIVINGAPARTMENTS_MEDI","LIVINGAREA_MEDI","NONLIVINGAPARTMENTS_MEDI","NONLIVINGAREA_MEDI","FONDKAPREMONT_MODE","HOUSETYPE_MODE","TOTALAREA_MODE","WALLSMATERIAL_MODE","EMERGENCYSTATE_MODE","OBS_30_CNT_SOCIAL_CIRCLE","DEF_30_CNT_SOCIAL_CIRCLE","OBS_60_CNT_SOCIAL_CIRCLE","DEF_60_CNT_SOCIAL_CIRCLE","DAYS_LAST_PHONE_CHANGE","FLAG_DOCUMENT_2","FLAG_DOCUMENT_3","FLAG_DOCUMENT_4","FLAG_DOCUMENT_5","FLAG_DOCUMENT_6","FLAG_DOCUMENT_7","FLAG_DOCUMENT_8","FLAG_DOCUMENT_9","FLAG_DOCUMENT_10","FLAG_DOCUMENT_11","FLAG_DOCUMENT_12","FLAG_DOCUMENT_13","FLAG_DOCUMENT_14","FLAG_DOCUMENT_15","FLAG_DOCUMENT_16","FLAG_DOCUMENT_17","FLAG_DOCUMENT_18","FLAG_DOCUMENT_19","FLAG_DOCUMENT_20","FLAG_DOCUMENT_21","AMT_REQ_CREDIT_BUREAU_HOUR","AMT_REQ_CREDIT_BUREAU_DAY","AMT_REQ_CREDIT_BUREAU_WEEK","AMT_REQ_CREDIT_BUREAU_MON","AMT_REQ_CREDIT_BUREAU_QRT","AMT_REQ_CREDIT_BUREAU_YEAR"],"feature_dtypes":{"NAME_CONTRACT_TYPE":"String","CODE_GENDER":"String","FLAG_OWN_CAR":"String","FLAG_OWN_REALTY":"String","CNT_CHILDREN":"Int64","AMT_INCOME_TOTAL":"Float64","AMT_ANNUITY":"Float64","AMT_GOODS_PRICE":"Float64","NAME_TYPE_SUITE":"String","NAME_INCOME_TYPE":"String","NAME_EDUCATION_TYPE":"String","NAME_FAMILY_STATUS":"String","NAME_HOUSING_TYPE":"String","REGION_POPULATION_RELATIVE":"Float64","DAYS_BIRTH":"Int64","DAYS_EMPLOYED":"Int64","DAYS_REGISTRATION":"Float64","DAYS_ID_PUBLISH":"Int64","OWN_CAR_AGE":"Float64","FLAG_MOBIL":"Int64","FLAG_EMP_PHONE":"Int64","FLAG_WORK_PHONE":"Int64","FLAG_CONT_MOBILE":"Int64","FLAG_PHONE":"Int64","FLAG_EMAIL":"Int64","OCCUPATION_TYPE":"String","CNT_FAM_MEMBERS":"Float64","REGION_RATING_CLIENT":"Int64","REGION_RATING_CLIENT_W_CITY":"Int64","WEEKDAY_APPR_PROCESS_START":"String","HOUR_APPR_PROCESS_START":"Int64","REG_REGION_NOT_LIVE_REGION":"Int64","REG_REGION_NOT_WORK_REGION":"Int64","LIVE_REGION_NOT_WORK_REGION":"Int64","REG_CITY_NOT_LIVE_CITY":"Int64","REG_CITY_NOT_WORK_CITY":"Int64","LIVE_CITY_NOT_WORK_CITY":"Int64","ORGANIZATION_TYPE":"String","EXT_SOURCE_1":"Float64","EXT_SOURCE_2":"Float64","EXT_SOURCE_3":"Float64","APARTMENTS_AVG":"Float64","BASEMENTAREA_AVG":"Float64","YEARS_BEGINEXPLUATATION_AVG":"Float64","YEARS_BUILD_AVG":"Float64","COMMONAREA_AVG":"Float64","ELEVATORS_AVG":"Float64","ENTRANCES_AVG":"Float64","FLOORSMAX_AVG":"Float64","FLOORSMIN_AVG":"Float64","LANDAREA_AVG":"Float64","LIVINGAPARTMENTS_AVG":"Float64","LIVINGAREA_AVG":"Float64","NONLIVINGAPARTMENTS_AVG":"Float64","NONLIVINGAREA_AVG":"Float64","APARTMENTS_MODE":"Float64","BASEMENTAREA_MODE":"Float64","YEARS_BEGINEXPLUATATION_MODE":"Float64","YEARS_BUILD_MODE":"Float64","COMMONAREA_MODE":"Float64","ELEVATORS_MODE":"Float64","ENTRANCES_MODE":"Float64","FLOORSMAX_MODE":"Float64","FLOORSMIN_MODE":"Float64","LANDAREA_MODE":"Float64","LIVINGAPARTMENTS_MODE":"Float64","LIVINGAREA_MODE":"Float64","NONLIVINGAPARTMENTS_MODE":"Float64","NONLIVINGAREA_MODE":"Float64","APARTMENTS_MEDI":"Float64","BASEMENTAREA_MEDI":"Float64","YEARS_BEGINEXPLUATATION_MEDI":"Float64","YEARS_BUILD_MEDI":"Float64","COMMONAREA_MEDI":"Float64","ELEVATORS_MEDI":"Float64","ENTRANCES_MEDI":"Float64","FLOORSMAX_MEDI":"Float64","FLOORSMIN_MEDI":"Float64","LANDAREA_MEDI":"Float64","LIVINGAPARTMENTS_MEDI":"Float64","LIVINGAREA_MEDI":"Float64","NONLIVINGAPARTMENTS_MEDI":"Float64","NONLIVINGAREA_MEDI":"Float64","FONDKAPREMONT_MODE":"String","HOUSETYPE_MODE":"String","TOTALAREA_MODE":"Float64","WALLSMATERIAL_MODE":"String","EMERGENCYSTATE_MODE":"String","OBS_30_CNT_SOCIAL_CIRCLE":"Float64","DEF_30_CNT_SOCIAL_CIRCLE":"Float64","OBS_60_CNT_SOCIAL_CIRCLE":"Float64","DEF_60_CNT_SOCIAL_CIRCLE":"Float64","DAYS_LAST_PHONE_CHANGE":"Float64","FLAG_DOCUMENT_2":"Int64","FLAG_DOCUMENT_3":"Int64","FLAG_DOCUMENT_4":"Int64","FLAG_DOCUMENT_5":"Int64","FLAG_DOCUMENT_6":"Int64","FLAG_DOCUMENT_7":"Int64","FLAG_DOCUMENT_8":"Int64","FLAG_DOCUMENT_9":"Int64","FLAG_DOCUMENT_10":"Int64","FLAG_DOCUMENT_11":"Int64","FLAG_DOCUMENT_12":"Int64","FLAG_DOCUMENT_13":"Int64","FLAG_DOCUMENT_14":"Int64","FLAG_DOCUMENT_15":"Int64","FLAG_DOCUMENT_16":"Int64","FLAG_DOCUMENT_17":"Int64","FLAG_DOCUMENT_18":"Int64","FLAG_DOCUMENT_19":"Int64","FLAG_DOCUMENT_20":"Int64","FLAG_DOCUMENT_21":"Int64","AMT_REQ_CREDIT_BUREAU_HOUR":"Float64","AMT_REQ_CREDIT_BUREAU_DAY":"Float64","AMT_REQ_CREDIT_BUREAU_WEEK":"Float64","AMT_REQ_CREDIT_BUREAU_MON":"Float64","AMT_REQ_CREDIT_BUREAU_QRT":"Float64","AMT_REQ_CREDIT_BUREAU_YEAR":"Float64"},"metrics":["missing","zeros","mean","psi"],"group_col":"dataset_flag","time_col":null,"time_grain":null,"benchmark_row_count":215374,"categorical_features":["NAME_CONTRACT_TYPE","CODE_GENDER","FLAG_OWN_CAR","FLAG_OWN_REALTY","NAME_TYPE_SUITE","NAME_INCOME_TYPE","NAME_EDUCATION_TYPE","NAME_FAMILY_STATUS","NAME_HOUSING_TYPE","OCCUPATION_TYPE","WEEKDAY_APPR_PROCESS_START","ORGANIZATION_TYPE","FONDKAPREMONT_MODE","HOUSETYPE_MODE","WALLSMATERIAL_MODE","EMERGENCYSTATE_MODE"],"profile_config":{"missing_values":[],"special_values":[],"overview_batch_size":500,"psi_batch_size":50,"psi_remove_empty_bins":true,"psi_merge_small_bins":true,"psi_min_bin_size":0.02,"psi_cv_ignore_threshold":0.05,"enable_sparkline":false,"sparkline_sample_size":200000,"sparkline_bins":8,"psi_n_bins":10,"psi_bin_method":"quantile","psi_include_missing":false,"psi_include_special":false},"diagnostics":[]}</t>
   </si>
   <si>
     <t>["只组织已有统计，未计算表不在目录中；失败和跳过见 parameters.diagnostics / fit_failures。","Null 不是数值 0；风险指标需结合标签表现状态，样本分布使用全样本。","比较前核对样本范围、权重、缺失/特殊箱、拟合来源、排序口径及参考来源；关联不代表因果。"]</t>
@@ -1237,7 +1237,7 @@
     <t>['NAME_CONTRACT_TYPE', 'CODE_GENDER', 'FLAG_OWN_CAR', 'FLAG_OWN_REALTY', 'CNT_CHILDREN', 'AMT_INCOME_TOTAL', 'AMT_ANNUITY', 'AMT_GOODS_PRICE', 'NAME_TYPE_SUITE', 'NAME_INCOME_TYPE', 'NAME_EDUCATION_TYPE', 'NAME_FAMILY_STATUS', 'NAME_HOUSING_TYPE', 'REGION_POPULATION_RELATIVE', 'DAYS_BIRTH', 'DAYS_EMPLOYED', 'DAYS_REGISTRATION', 'DAYS_ID_PUBLISH', 'OWN_CAR_AGE', 'FLAG_MOBIL', 'FLAG_EMP_PHONE', 'FLAG_WORK_PHONE', 'FLAG_CONT_MOBILE', 'FLAG_PHONE', 'FLAG_EMAIL', 'OCCUPATION_TYPE', 'CNT_FAM_MEMBERS', 'REGION_RATING_CLIENT', 'REGION_RATING_CLIENT_W_CITY', 'WEEKDAY_APPR_PROCESS_START', 'HOUR_APPR_PROCESS_START', 'REG_REGION_NOT_LIVE_REGION', 'REG_REGION_NOT_WORK_REGION', 'LIVE_REGION_NOT_WORK_REGION', 'REG_CITY_NOT_LIVE_CITY', 'REG_CITY_NOT_WORK_CITY', 'LIVE_CITY_NOT_WORK_CITY', 'ORGANIZATION_TYPE', 'EXT_SOURCE_1', 'EXT_SOURCE_2', 'EXT_SOURCE_3', 'APARTMENTS_AVG', 'BASEMENTAREA_AVG', 'YEARS_BEGINEXPLUATATION_AVG', 'YEARS_BUILD_AVG', 'COMMONAREA_AVG', 'ELEVATORS_AVG', 'ENTRANCES_AVG', 'FLOORSMAX_AVG', 'FLOORSMIN_AVG', 'LANDAREA_AVG', 'LIVINGAPARTMENTS_AVG', 'LIVINGAREA_AVG', 'NONLIVINGAPARTMENTS_AVG', 'NONLIVINGAREA_AVG', 'APARTMENTS_MODE', 'BASEMENTAREA_MODE', 'YEARS_BEGINEXPLUATATION_MODE', 'YEARS_BUILD_MODE', 'COMMONAREA_MODE', 'ELEVATORS_MODE', 'ENTRANCES_MODE', 'FLOORSMAX_MODE', 'FLOORSMIN_MODE', 'LANDAREA_MODE', 'LIVINGAPARTMENTS_MODE', 'LIVINGAREA_MODE', 'NONLIVINGAPARTMENTS_MODE', 'NONLIVINGAREA_MODE', 'APARTMENTS_MEDI', 'BASEMENTAREA_MEDI', 'YEARS_BEGINEXPLUATATION_MEDI', 'YEARS_BUILD_MEDI', 'COMMONAREA_MEDI', 'ELEVATORS_MEDI', 'ENTRANCES_MEDI', 'FLOORSMAX_MEDI', 'FLOORSMIN_MEDI', 'LANDAREA_MEDI', 'LIVINGAPARTMENTS_MEDI', 'LIVINGAREA_MEDI', 'NONLIVINGAPARTMENTS_MEDI', 'NONLIVINGAREA_MEDI', 'FONDKAPREMONT_MODE', 'HOUSETYPE_MODE', 'TOTALAREA_MODE', 'WALLSMATERIAL_MODE', 'EMERGENCYSTATE_MODE', 'OBS_30_CNT_SOCIAL_CIRCLE', 'DEF_30_CNT_SOCIAL_CIRCLE', 'OBS_60_CNT_SOCIAL_CIRCLE', 'DEF_60_CNT_SOCIAL_CIRCLE', 'DAYS_LAST_PHONE_CHANGE', 'FLAG_DOCUMENT_2', 'FLAG_DOCUMENT_3', 'FLAG_DOCUMENT_4', 'FLAG_DOCUMENT_5', 'FLAG_DOCUMENT_6', 'FLAG_DOCUMENT_7', 'FLAG_DOCUMENT_8', 'FLAG_DOCUMENT_9', 'FLAG_DOCUMENT_10', 'FLAG_DOCUMENT_11', 'FLAG_DOCUMENT_12', 'FLAG_DOCUMENT_13', 'FLAG_DOCUMENT_14', 'FLAG_DOCUMENT_15', 'FLAG_DOCUMENT_16', 'FLAG_DOCUMENT_17', 'FLAG_DOCUMENT_18', 'FLAG_DOCUMENT_19', 'FLAG_DOCUMENT_20', 'FLAG_DOCUMENT_21', 'AMT_REQ_CREDIT_BUREAU_HOUR', 'AMT_REQ_CREDIT_BUREAU_DAY', 'AMT_REQ_CREDIT_BUREAU_WEEK', 'AMT_REQ_CREDIT_BUREAU_MON', 'AMT_REQ_CREDIT_BUREAU_QRT', 'AMT_REQ_CREDIT_BUREAU_YEAR']</t>
   </si>
   <si>
-    <t>2026-10-15T14:46:46.380326+00:00</t>
+    <t>2026-10-22T15:04:08.748771+00:00</t>
   </si>
   <si>
     <t>dataset_flag</t>
@@ -5319,16 +5319,16 @@
         <v>0</v>
       </c>
       <c r="F6" s="146">
-        <v>0.0002726746719591321</v>
+        <v>0.000272674671959132</v>
       </c>
       <c r="G6" s="146">
         <v>0.0004359908872592861</v>
       </c>
       <c r="H6" s="146">
-        <v>0.0001317530575212158</v>
+        <v>0.0001317530575212157</v>
       </c>
       <c r="I6" s="153">
-        <v>0.07906116106137594</v>
+        <v>0.07906116106137592</v>
       </c>
       <c r="J6" s="146">
         <v>0.001365279438322753</v>
@@ -5351,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="146">
-        <v>0.0004229575247267527</v>
+        <v>0.0004229575247267528</v>
       </c>
       <c r="G7" s="146">
         <v>0.0004568298256773325</v>
@@ -5389,10 +5389,10 @@
         <v>0.0001775186430226059</v>
       </c>
       <c r="H8" s="146">
-        <v>0.0003406410569698185</v>
+        <v>0.0003406410569698186</v>
       </c>
       <c r="I8" s="154">
-        <v>0.06733499123360269</v>
+        <v>0.06733499123360268</v>
       </c>
       <c r="J8" s="146">
         <v>0.001132385811507225</v>
@@ -5418,16 +5418,16 @@
         <v>0.0006750568107998361</v>
       </c>
       <c r="G9" s="146">
-        <v>0.001165957983750373</v>
+        <v>0.001165957983750372</v>
       </c>
       <c r="H9" s="146">
         <v>0.0007635089613454508</v>
       </c>
       <c r="I9" s="155">
-        <v>0.05393939544735974</v>
+        <v>0.05393939544735973</v>
       </c>
       <c r="J9" s="146">
-        <v>0.000957399880479347</v>
+        <v>0.0009573998804793469</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -5450,16 +5450,16 @@
         <v>0.000523830081062208</v>
       </c>
       <c r="G10" s="146">
-        <v>0.0003435973883749283</v>
+        <v>0.0003435973883749282</v>
       </c>
       <c r="H10" s="146">
-        <v>0.0002656958730702189</v>
+        <v>0.0002656958730702188</v>
       </c>
       <c r="I10" s="156">
         <v>0.03332165477534482</v>
       </c>
       <c r="J10" s="146">
-        <v>0.0006962704742667549</v>
+        <v>0.000696270474266755</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -5543,19 +5543,19 @@
         <v>0</v>
       </c>
       <c r="F13" s="146">
-        <v>0.000291704025957037</v>
+        <v>0.0002917040259570371</v>
       </c>
       <c r="G13" s="146">
         <v>0.0003695330754674947</v>
       </c>
       <c r="H13" s="146">
-        <v>0.0001648096561912275</v>
+        <v>0.0001648096561912276</v>
       </c>
       <c r="I13" s="159">
         <v>0.02041594532379953</v>
       </c>
       <c r="J13" s="146">
-        <v>0.0003866534087206919</v>
+        <v>0.000386653408720692</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -5613,7 +5613,7 @@
         <v>0.0005673208372032511</v>
       </c>
       <c r="H15" s="146">
-        <v>0.0008164301070808326</v>
+        <v>0.0008164301070808327</v>
       </c>
       <c r="I15" s="161">
         <v>0.004706356609441836</v>
@@ -5639,7 +5639,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="146">
-        <v>0.0009046902798901654</v>
+        <v>0.0009046902798901655</v>
       </c>
       <c r="G16" s="146">
         <v>0.0006650050198618814</v>
@@ -5671,7 +5671,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="146">
-        <v>0.0001096565426844394</v>
+        <v>0.0001096565426844393</v>
       </c>
       <c r="G17" s="146">
         <v>0.0002116832694920014</v>
@@ -5703,13 +5703,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="146">
-        <v>0.001650933059097768</v>
+        <v>0.001650933059097767</v>
       </c>
       <c r="G18" s="146">
-        <v>0.0008336962051746353</v>
+        <v>0.0008336962051746352</v>
       </c>
       <c r="H18" s="146">
-        <v>0.0007278830184852887</v>
+        <v>0.0007278830184852888</v>
       </c>
       <c r="I18" s="161">
         <v>0.004137764121160776</v>
@@ -5735,16 +5735,16 @@
         <v>0</v>
       </c>
       <c r="F19" s="146">
-        <v>0.0004556121891369468</v>
+        <v>0.0004556121891369469</v>
       </c>
       <c r="G19" s="146">
-        <v>0.0005330953972298456</v>
+        <v>0.0005330953972298455</v>
       </c>
       <c r="H19" s="146">
         <v>0.0004706421867144862</v>
       </c>
       <c r="I19" s="161">
-        <v>0.005354227639334085</v>
+        <v>0.005354227639334084</v>
       </c>
       <c r="J19" s="146">
         <v>0.0001678403130814548</v>
@@ -5779,7 +5779,7 @@
         <v>0.006946798164662937</v>
       </c>
       <c r="J20" s="146">
-        <v>0.0001499710901522096</v>
+        <v>0.0001499710901522095</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5811,7 +5811,7 @@
         <v>0.00656310634109442</v>
       </c>
       <c r="J21" s="146">
-        <v>0.000147023007573291</v>
+        <v>0.0001470230075732909</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -5831,16 +5831,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="146">
-        <v>0.0009006046387112045</v>
+        <v>0.0009006046387112046</v>
       </c>
       <c r="G22" s="146">
         <v>0.0007769785026426631</v>
       </c>
       <c r="H22" s="146">
-        <v>0.0006726731336210813</v>
+        <v>0.0006726731336210814</v>
       </c>
       <c r="I22" s="150">
-        <v>0.003330570546054684</v>
+        <v>0.003330570546054685</v>
       </c>
       <c r="J22" s="146">
         <v>0.0001435186658435046</v>
@@ -5863,10 +5863,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="146">
-        <v>0.0009935288958555514</v>
+        <v>0.0009935288958555517</v>
       </c>
       <c r="G23" s="146">
-        <v>0.0007391243637027697</v>
+        <v>0.0007391243637027696</v>
       </c>
       <c r="H23" s="146">
         <v>0.0006388049920837873</v>
@@ -5898,10 +5898,10 @@
         <v>0.001272906562277207</v>
       </c>
       <c r="G24" s="146">
-        <v>0.0008823029735659297</v>
+        <v>0.0008823029735659298</v>
       </c>
       <c r="H24" s="146">
-        <v>0.000665691965774721</v>
+        <v>0.0006656919657747209</v>
       </c>
       <c r="I24" s="150">
         <v>0.002985011706108473</v>
@@ -5927,13 +5927,13 @@
         <v>0</v>
       </c>
       <c r="F25" s="146">
-        <v>0.001361777816957066</v>
+        <v>0.001361777816957065</v>
       </c>
       <c r="G25" s="146">
-        <v>0.0005540000586823032</v>
+        <v>0.0005540000586823034</v>
       </c>
       <c r="H25" s="146">
-        <v>0.0004075110544693657</v>
+        <v>0.0004075110544693656</v>
       </c>
       <c r="I25" s="150">
         <v>0.003201573821348539</v>
@@ -5991,16 +5991,16 @@
         <v>0</v>
       </c>
       <c r="F27" s="146">
-        <v>0.0009633003282023781</v>
+        <v>0.0009633003282023779</v>
       </c>
       <c r="G27" s="146">
         <v>0.0006349675527692761</v>
       </c>
       <c r="H27" s="146">
-        <v>0.000625639600237944</v>
+        <v>0.0006256396002379441</v>
       </c>
       <c r="I27" s="150">
-        <v>0.002022172535249798</v>
+        <v>0.002022172535249797</v>
       </c>
       <c r="J27" s="146">
         <v>0.0001163316398745226</v>
@@ -6026,13 +6026,13 @@
         <v>0.001652053173011206</v>
       </c>
       <c r="G28" s="146">
-        <v>0.0008782617878327254</v>
+        <v>0.0008782617878327252</v>
       </c>
       <c r="H28" s="146">
-        <v>0.0007356732431974096</v>
+        <v>0.0007356732431974095</v>
       </c>
       <c r="I28" s="150">
-        <v>0.003084644650046324</v>
+        <v>0.003084644650046323</v>
       </c>
       <c r="J28" s="146">
         <v>0.0001114084653095748</v>
@@ -6064,7 +6064,7 @@
         <v>0.0002394331653234997</v>
       </c>
       <c r="I29" s="148">
-        <v>0.006376492008095778</v>
+        <v>0.006376492008095779</v>
       </c>
       <c r="J29" s="146">
         <v>0.000108165771738073</v>
@@ -6119,16 +6119,16 @@
         <v>0</v>
       </c>
       <c r="F31" s="146">
-        <v>0.0005089967561114184</v>
+        <v>0.0005089967561114183</v>
       </c>
       <c r="G31" s="146">
         <v>0.0003009977067106791</v>
       </c>
       <c r="H31" s="146">
-        <v>0.000384652839349121</v>
+        <v>0.0003846528393491211</v>
       </c>
       <c r="I31" s="150">
-        <v>0.003224877183890442</v>
+        <v>0.003224877183890443</v>
       </c>
       <c r="J31" s="146">
         <v>0.0001021199073248556</v>
@@ -6157,7 +6157,7 @@
         <v>0.0006818970645536205</v>
       </c>
       <c r="H32" s="146">
-        <v>0.0007319317012882109</v>
+        <v>0.000731931701288211</v>
       </c>
       <c r="I32" s="150">
         <v>0.002500133019511184</v>
@@ -6186,10 +6186,10 @@
         <v>0.0007512884389942388</v>
       </c>
       <c r="G33" s="146">
-        <v>0.0004671529086438923</v>
+        <v>0.0004671529086438922</v>
       </c>
       <c r="H33" s="146">
-        <v>0.0005392374509245958</v>
+        <v>0.0005392374509245959</v>
       </c>
       <c r="I33" s="146">
         <v>0.001928759584783809</v>
@@ -6250,7 +6250,7 @@
         <v>0.0005333747214542877</v>
       </c>
       <c r="G35" s="146">
-        <v>0.0006819780493090346</v>
+        <v>0.0006819780493090345</v>
       </c>
       <c r="H35" s="146">
         <v>0.0009777852959205031</v>
@@ -6259,7 +6259,7 @@
         <v>0.002122144540446974</v>
       </c>
       <c r="J35" s="146">
-        <v>9.607204679871793E-05</v>
+        <v>9.607204679871796E-05</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -6285,13 +6285,13 @@
         <v>0.0003294849134768536</v>
       </c>
       <c r="H36" s="146">
-        <v>0.0003514020916553111</v>
+        <v>0.000351402091655311</v>
       </c>
       <c r="I36" s="150">
         <v>0.003027728072991942</v>
       </c>
       <c r="J36" s="146">
-        <v>9.485598193598407E-05</v>
+        <v>9.485598193598406E-05</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -6317,7 +6317,7 @@
         <v>0.000241534845296256</v>
       </c>
       <c r="H37" s="146">
-        <v>0.000370102232075577</v>
+        <v>0.0003701022320755771</v>
       </c>
       <c r="I37" s="150">
         <v>0.003018147735022604</v>
@@ -6355,7 +6355,7 @@
         <v>0.003251192310346166</v>
       </c>
       <c r="J38" s="146">
-        <v>9.05820018456557E-05</v>
+        <v>9.058200184565569E-05</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -6381,7 +6381,7 @@
         <v>0.000898709661868989</v>
       </c>
       <c r="H39" s="146">
-        <v>0.0008045020086613745</v>
+        <v>0.0008045020086613746</v>
       </c>
       <c r="I39" s="150">
         <v>0.003399327545300172</v>
@@ -6442,10 +6442,10 @@
         <v>0.0009875491174354983</v>
       </c>
       <c r="G41" s="146">
-        <v>0.0005831103459684678</v>
+        <v>0.0005831103459684677</v>
       </c>
       <c r="H41" s="146">
-        <v>0.0006929788320388084</v>
+        <v>0.0006929788320388085</v>
       </c>
       <c r="I41" s="146">
         <v>0.00178602262560277</v>
@@ -6515,7 +6515,7 @@
         <v>0.003417311686465374</v>
       </c>
       <c r="J43" s="146">
-        <v>7.669878535224095E-05</v>
+        <v>7.669878535224097E-05</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -6535,13 +6535,13 @@
         <v>0</v>
       </c>
       <c r="F44" s="146">
-        <v>0.0006518714142455467</v>
+        <v>0.0006518714142455465</v>
       </c>
       <c r="G44" s="146">
         <v>0.000754099084926538</v>
       </c>
       <c r="H44" s="146">
-        <v>0.0006955018235551966</v>
+        <v>0.0006955018235551968</v>
       </c>
       <c r="I44" s="150">
         <v>0.00204539480717465</v>
@@ -6570,10 +6570,10 @@
         <v>0.0004061210446586284</v>
       </c>
       <c r="G45" s="146">
-        <v>0.0006415378609272537</v>
+        <v>0.0006415378609272536</v>
       </c>
       <c r="H45" s="146">
-        <v>0.0004536670363327289</v>
+        <v>0.000453667036332729</v>
       </c>
       <c r="I45" s="146">
         <v>0.00182207547862773</v>
@@ -6599,19 +6599,19 @@
         <v>0</v>
       </c>
       <c r="F46" s="146">
-        <v>0.0003859949364064136</v>
+        <v>0.0003859949364064137</v>
       </c>
       <c r="G46" s="146">
         <v>0.0002773173745272085</v>
       </c>
       <c r="H46" s="146">
-        <v>0.0008791763185465448</v>
+        <v>0.0008791763185465449</v>
       </c>
       <c r="I46" s="146">
         <v>0.001037007379557002</v>
       </c>
       <c r="J46" s="146">
-        <v>6.815672617542395E-05</v>
+        <v>6.815672617542394E-05</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -6637,7 +6637,7 @@
         <v>0.0001502002697825659</v>
       </c>
       <c r="H47" s="146">
-        <v>0.0003391001223749199</v>
+        <v>0.00033910012237492</v>
       </c>
       <c r="I47" s="146">
         <v>0.001930994764990302</v>
@@ -6669,7 +6669,7 @@
         <v>0.0003938379231976477</v>
       </c>
       <c r="H48" s="146">
-        <v>0.0007092755957732805</v>
+        <v>0.0007092755957732804</v>
       </c>
       <c r="I48" s="146">
         <v>0.001112067799557301</v>
@@ -6727,7 +6727,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="146">
-        <v>0.0002934314362116992</v>
+        <v>0.0002934314362116993</v>
       </c>
       <c r="G50" s="146">
         <v>0.0004116445508652776</v>
@@ -6765,13 +6765,13 @@
         <v>0.0007281361170196919</v>
       </c>
       <c r="H51" s="146">
-        <v>0.0007769784503198827</v>
+        <v>0.0007769784503198826</v>
       </c>
       <c r="I51" s="150">
         <v>0.003197524760845585</v>
       </c>
       <c r="J51" s="146">
-        <v>5.733106928010409E-05</v>
+        <v>5.73310692801041E-05</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -6794,7 +6794,7 @@
         <v>5.162554495058317E-05</v>
       </c>
       <c r="G52" s="146">
-        <v>8.327574286197291E-05</v>
+        <v>8.32757428619729E-05</v>
       </c>
       <c r="H52" s="146">
         <v>2.491994902119042E-05</v>
@@ -6826,7 +6826,7 @@
         <v>0.00146294832796287</v>
       </c>
       <c r="G53" s="146">
-        <v>0.0009279497017872705</v>
+        <v>0.0009279497017872704</v>
       </c>
       <c r="H53" s="146">
         <v>0.000934498532420981</v>
@@ -6858,7 +6858,7 @@
         <v>0.001303302069239048</v>
       </c>
       <c r="G54" s="146">
-        <v>0.0007867452271667024</v>
+        <v>0.0007867452271667025</v>
       </c>
       <c r="H54" s="146">
         <v>0.0009034028994133381</v>
@@ -6867,7 +6867,7 @@
         <v>0.003673183179908199</v>
       </c>
       <c r="J54" s="146">
-        <v>5.280395853889536E-05</v>
+        <v>5.280395853889535E-05</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -6928,10 +6928,10 @@
         <v>0.0002264901334634941</v>
       </c>
       <c r="I56" s="146">
-        <v>0.0007588016769100851</v>
+        <v>0.000758801676910085</v>
       </c>
       <c r="J56" s="146">
-        <v>5.180834988266438E-05</v>
+        <v>5.180834988266439E-05</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -6951,10 +6951,10 @@
         <v>0</v>
       </c>
       <c r="F57" s="146">
-        <v>0.0007974564453622556</v>
+        <v>0.0007974564453622557</v>
       </c>
       <c r="G57" s="146">
-        <v>7.340040586765771E-05</v>
+        <v>7.34004058676577E-05</v>
       </c>
       <c r="H57" s="146">
         <v>0.0001350336952345964</v>
@@ -7015,13 +7015,13 @@
         <v>0</v>
       </c>
       <c r="F59" s="146">
-        <v>0.0002069888926426199</v>
+        <v>0.0002069888926426198</v>
       </c>
       <c r="G59" s="146">
         <v>0.0001608385656067654</v>
       </c>
       <c r="H59" s="146">
-        <v>0.0002762886130491056</v>
+        <v>0.0002762886130491055</v>
       </c>
       <c r="I59" s="146">
         <v>0.001574545841507414</v>
@@ -7047,13 +7047,13 @@
         <v>0</v>
       </c>
       <c r="F60" s="146">
-        <v>0.001794487276278081</v>
+        <v>0.00179448727627808</v>
       </c>
       <c r="G60" s="146">
-        <v>0.001149722071685594</v>
+        <v>0.001149722071685593</v>
       </c>
       <c r="H60" s="146">
-        <v>0.0007402241373375571</v>
+        <v>0.000740224137337557</v>
       </c>
       <c r="I60" s="150">
         <v>0.003761064181919265</v>
@@ -7114,7 +7114,7 @@
         <v>0.0001388867730216045</v>
       </c>
       <c r="G62" s="146">
-        <v>0.0004361603140427749</v>
+        <v>0.000436160314042775</v>
       </c>
       <c r="H62" s="146">
         <v>0.0002174930525808354</v>
@@ -7152,10 +7152,10 @@
         <v>0.000273187867631693</v>
       </c>
       <c r="I63" s="146">
-        <v>0.001476868876091028</v>
+        <v>0.001476868876091027</v>
       </c>
       <c r="J63" s="146">
-        <v>4.474591106952164E-05</v>
+        <v>4.474591106952166E-05</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -7274,7 +7274,7 @@
         <v>0.0001203327264306773</v>
       </c>
       <c r="G67" s="146">
-        <v>0.0006928895512978086</v>
+        <v>0.0006928895512978085</v>
       </c>
       <c r="H67" s="146">
         <v>0.0001965028563277855</v>
@@ -7306,16 +7306,16 @@
         <v>0.0007461572027814187</v>
       </c>
       <c r="G68" s="146">
-        <v>0.0006544961187338145</v>
+        <v>0.0006544961187338143</v>
       </c>
       <c r="H68" s="146">
         <v>0.000350644640923031</v>
       </c>
       <c r="I68" s="146">
-        <v>0.000902903176290073</v>
+        <v>0.0009029031762900729</v>
       </c>
       <c r="J68" s="146">
-        <v>3.512182112597061E-05</v>
+        <v>3.512182112597062E-05</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -7399,7 +7399,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="146">
-        <v>0.0003078336390633141</v>
+        <v>0.000307833639063314</v>
       </c>
       <c r="G71" s="146">
         <v>0.0004032891911680437</v>
@@ -7463,7 +7463,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="146">
-        <v>4.9223375638132E-05</v>
+        <v>4.922337563813201E-05</v>
       </c>
       <c r="G73" s="146">
         <v>0.0003075762294441428</v>
@@ -7559,7 +7559,7 @@
         <v>0</v>
       </c>
       <c r="F76" s="146">
-        <v>0.0004761382144854724</v>
+        <v>0.0004761382144854723</v>
       </c>
       <c r="G76" s="146">
         <v>0.0006350778082566487</v>
@@ -7568,7 +7568,7 @@
         <v>0.0005807056819354495</v>
       </c>
       <c r="I76" s="146">
-        <v>0.0007993558356615606</v>
+        <v>0.0007993558356615605</v>
       </c>
       <c r="J76" s="146">
         <v>2.204468229393618E-05</v>
@@ -7629,7 +7629,7 @@
         <v>9.690726814371819E-05</v>
       </c>
       <c r="H78" s="146">
-        <v>7.339412510548933E-05</v>
+        <v>7.339412510548932E-05</v>
       </c>
       <c r="I78" s="146">
         <v>0.0008353536601565182</v>
@@ -7655,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="146">
-        <v>0.0005781458001414296</v>
+        <v>0.0005781458001414297</v>
       </c>
       <c r="G79" s="146">
         <v>0.0001843307801176307</v>
@@ -7664,7 +7664,7 @@
         <v>2.736757282872682E-05</v>
       </c>
       <c r="I79" s="146">
-        <v>0.0008294003371478876</v>
+        <v>0.0008294003371478877</v>
       </c>
       <c r="J79" s="146">
         <v>1.957414016171001E-05</v>
@@ -7792,7 +7792,7 @@
         <v>0.0003501664781923937</v>
       </c>
       <c r="I83" s="146">
-        <v>0.0003739191734389025</v>
+        <v>0.0003739191734389024</v>
       </c>
       <c r="J83" s="146">
         <v>9.803484471619088E-06</v>
@@ -7920,7 +7920,7 @@
         <v>0.0006673784490667053</v>
       </c>
       <c r="I87" s="146">
-        <v>4.410448904972119E-05</v>
+        <v>4.410448904972118E-05</v>
       </c>
       <c r="J87" s="146">
         <v>4.50903366754307E-06</v>
@@ -7943,7 +7943,7 @@
         <v>0</v>
       </c>
       <c r="F88" s="146">
-        <v>0.0001030651974179946</v>
+        <v>0.0001030651974179945</v>
       </c>
       <c r="G88" s="146">
         <v>0.0002225085141382576</v>
@@ -7952,7 +7952,7 @@
         <v>0.0001580613216774258</v>
       </c>
       <c r="I88" s="146">
-        <v>2.613720564824346E-05</v>
+        <v>2.613720564824345E-05</v>
       </c>
       <c r="J88" s="146">
         <v>3.743291536592727E-06</v>
@@ -8074,7 +8074,7 @@
         <v>0.0001138493828187559</v>
       </c>
       <c r="G92" s="146">
-        <v>0.0001789457619515659</v>
+        <v>0.0001789457619515658</v>
       </c>
       <c r="H92" s="146">
         <v>0.0001229179670342798</v>

--- a/docs/assets/cases/profile.xlsx
+++ b/docs/assets/cases/profile.xlsx
@@ -1120,7 +1120,7 @@
     <t>"MarsProfileReport"</t>
   </si>
   <si>
-    <t>"39fae55f-e3a7-4d88-86b2-edcdb1d533dd"</t>
+    <t>"fef9a614-488e-424e-b644-a0c54aa1432f"</t>
   </si>
   <si>
     <t>1</t>
@@ -1141,7 +1141,7 @@
     <t>{"table":"calculation_status","diagnostics":"parameters.diagnostics/fit_failures/raw_ks_diagnostics","scope":"feature/target/group/metric; profile status contains exceptional outcomes only, not all trend cells"}</t>
   </si>
   <si>
-    <t>{"mars_version":"0.0.28","polars_version":"1.42.0","generated_at_utc":"2026-10-22T15:04:08.748771+00:00","input_type":"polars","row_count":356255,"column_count":124,"features":["NAME_CONTRACT_TYPE","CODE_GENDER","FLAG_OWN_CAR","FLAG_OWN_REALTY","CNT_CHILDREN","AMT_INCOME_TOTAL","AMT_ANNUITY","AMT_GOODS_PRICE","NAME_TYPE_SUITE","NAME_INCOME_TYPE","NAME_EDUCATION_TYPE","NAME_FAMILY_STATUS","NAME_HOUSING_TYPE","REGION_POPULATION_RELATIVE","DAYS_BIRTH","DAYS_EMPLOYED","DAYS_REGISTRATION","DAYS_ID_PUBLISH","OWN_CAR_AGE","FLAG_MOBIL","FLAG_EMP_PHONE","FLAG_WORK_PHONE","FLAG_CONT_MOBILE","FLAG_PHONE","FLAG_EMAIL","OCCUPATION_TYPE","CNT_FAM_MEMBERS","REGION_RATING_CLIENT","REGION_RATING_CLIENT_W_CITY","WEEKDAY_APPR_PROCESS_START","HOUR_APPR_PROCESS_START","REG_REGION_NOT_LIVE_REGION","REG_REGION_NOT_WORK_REGION","LIVE_REGION_NOT_WORK_REGION","REG_CITY_NOT_LIVE_CITY","REG_CITY_NOT_WORK_CITY","LIVE_CITY_NOT_WORK_CITY","ORGANIZATION_TYPE","EXT_SOURCE_1","EXT_SOURCE_2","EXT_SOURCE_3","APARTMENTS_AVG","BASEMENTAREA_AVG","YEARS_BEGINEXPLUATATION_AVG","YEARS_BUILD_AVG","COMMONAREA_AVG","ELEVATORS_AVG","ENTRANCES_AVG","FLOORSMAX_AVG","FLOORSMIN_AVG","LANDAREA_AVG","LIVINGAPARTMENTS_AVG","LIVINGAREA_AVG","NONLIVINGAPARTMENTS_AVG","NONLIVINGAREA_AVG","APARTMENTS_MODE","BASEMENTAREA_MODE","YEARS_BEGINEXPLUATATION_MODE","YEARS_BUILD_MODE","COMMONAREA_MODE","ELEVATORS_MODE","ENTRANCES_MODE","FLOORSMAX_MODE","FLOORSMIN_MODE","LANDAREA_MODE","LIVINGAPARTMENTS_MODE","LIVINGAREA_MODE","NONLIVINGAPARTMENTS_MODE","NONLIVINGAREA_MODE","APARTMENTS_MEDI","BASEMENTAREA_MEDI","YEARS_BEGINEXPLUATATION_MEDI","YEARS_BUILD_MEDI","COMMONAREA_MEDI","ELEVATORS_MEDI","ENTRANCES_MEDI","FLOORSMAX_MEDI","FLOORSMIN_MEDI","LANDAREA_MEDI","LIVINGAPARTMENTS_MEDI","LIVINGAREA_MEDI","NONLIVINGAPARTMENTS_MEDI","NONLIVINGAREA_MEDI","FONDKAPREMONT_MODE","HOUSETYPE_MODE","TOTALAREA_MODE","WALLSMATERIAL_MODE","EMERGENCYSTATE_MODE","OBS_30_CNT_SOCIAL_CIRCLE","DEF_30_CNT_SOCIAL_CIRCLE","OBS_60_CNT_SOCIAL_CIRCLE","DEF_60_CNT_SOCIAL_CIRCLE","DAYS_LAST_PHONE_CHANGE","FLAG_DOCUMENT_2","FLAG_DOCUMENT_3","FLAG_DOCUMENT_4","FLAG_DOCUMENT_5","FLAG_DOCUMENT_6","FLAG_DOCUMENT_7","FLAG_DOCUMENT_8","FLAG_DOCUMENT_9","FLAG_DOCUMENT_10","FLAG_DOCUMENT_11","FLAG_DOCUMENT_12","FLAG_DOCUMENT_13","FLAG_DOCUMENT_14","FLAG_DOCUMENT_15","FLAG_DOCUMENT_16","FLAG_DOCUMENT_17","FLAG_DOCUMENT_18","FLAG_DOCUMENT_19","FLAG_DOCUMENT_20","FLAG_DOCUMENT_21","AMT_REQ_CREDIT_BUREAU_HOUR","AMT_REQ_CREDIT_BUREAU_DAY","AMT_REQ_CREDIT_BUREAU_WEEK","AMT_REQ_CREDIT_BUREAU_MON","AMT_REQ_CREDIT_BUREAU_QRT","AMT_REQ_CREDIT_BUREAU_YEAR"],"feature_dtypes":{"NAME_CONTRACT_TYPE":"String","CODE_GENDER":"String","FLAG_OWN_CAR":"String","FLAG_OWN_REALTY":"String","CNT_CHILDREN":"Int64","AMT_INCOME_TOTAL":"Float64","AMT_ANNUITY":"Float64","AMT_GOODS_PRICE":"Float64","NAME_TYPE_SUITE":"String","NAME_INCOME_TYPE":"String","NAME_EDUCATION_TYPE":"String","NAME_FAMILY_STATUS":"String","NAME_HOUSING_TYPE":"String","REGION_POPULATION_RELATIVE":"Float64","DAYS_BIRTH":"Int64","DAYS_EMPLOYED":"Int64","DAYS_REGISTRATION":"Float64","DAYS_ID_PUBLISH":"Int64","OWN_CAR_AGE":"Float64","FLAG_MOBIL":"Int64","FLAG_EMP_PHONE":"Int64","FLAG_WORK_PHONE":"Int64","FLAG_CONT_MOBILE":"Int64","FLAG_PHONE":"Int64","FLAG_EMAIL":"Int64","OCCUPATION_TYPE":"String","CNT_FAM_MEMBERS":"Float64","REGION_RATING_CLIENT":"Int64","REGION_RATING_CLIENT_W_CITY":"Int64","WEEKDAY_APPR_PROCESS_START":"String","HOUR_APPR_PROCESS_START":"Int64","REG_REGION_NOT_LIVE_REGION":"Int64","REG_REGION_NOT_WORK_REGION":"Int64","LIVE_REGION_NOT_WORK_REGION":"Int64","REG_CITY_NOT_LIVE_CITY":"Int64","REG_CITY_NOT_WORK_CITY":"Int64","LIVE_CITY_NOT_WORK_CITY":"Int64","ORGANIZATION_TYPE":"String","EXT_SOURCE_1":"Float64","EXT_SOURCE_2":"Float64","EXT_SOURCE_3":"Float64","APARTMENTS_AVG":"Float64","BASEMENTAREA_AVG":"Float64","YEARS_BEGINEXPLUATATION_AVG":"Float64","YEARS_BUILD_AVG":"Float64","COMMONAREA_AVG":"Float64","ELEVATORS_AVG":"Float64","ENTRANCES_AVG":"Float64","FLOORSMAX_AVG":"Float64","FLOORSMIN_AVG":"Float64","LANDAREA_AVG":"Float64","LIVINGAPARTMENTS_AVG":"Float64","LIVINGAREA_AVG":"Float64","NONLIVINGAPARTMENTS_AVG":"Float64","NONLIVINGAREA_AVG":"Float64","APARTMENTS_MODE":"Float64","BASEMENTAREA_MODE":"Float64","YEARS_BEGINEXPLUATATION_MODE":"Float64","YEARS_BUILD_MODE":"Float64","COMMONAREA_MODE":"Float64","ELEVATORS_MODE":"Float64","ENTRANCES_MODE":"Float64","FLOORSMAX_MODE":"Float64","FLOORSMIN_MODE":"Float64","LANDAREA_MODE":"Float64","LIVINGAPARTMENTS_MODE":"Float64","LIVINGAREA_MODE":"Float64","NONLIVINGAPARTMENTS_MODE":"Float64","NONLIVINGAREA_MODE":"Float64","APARTMENTS_MEDI":"Float64","BASEMENTAREA_MEDI":"Float64","YEARS_BEGINEXPLUATATION_MEDI":"Float64","YEARS_BUILD_MEDI":"Float64","COMMONAREA_MEDI":"Float64","ELEVATORS_MEDI":"Float64","ENTRANCES_MEDI":"Float64","FLOORSMAX_MEDI":"Float64","FLOORSMIN_MEDI":"Float64","LANDAREA_MEDI":"Float64","LIVINGAPARTMENTS_MEDI":"Float64","LIVINGAREA_MEDI":"Float64","NONLIVINGAPARTMENTS_MEDI":"Float64","NONLIVINGAREA_MEDI":"Float64","FONDKAPREMONT_MODE":"String","HOUSETYPE_MODE":"String","TOTALAREA_MODE":"Float64","WALLSMATERIAL_MODE":"String","EMERGENCYSTATE_MODE":"String","OBS_30_CNT_SOCIAL_CIRCLE":"Float64","DEF_30_CNT_SOCIAL_CIRCLE":"Float64","OBS_60_CNT_SOCIAL_CIRCLE":"Float64","DEF_60_CNT_SOCIAL_CIRCLE":"Float64","DAYS_LAST_PHONE_CHANGE":"Float64","FLAG_DOCUMENT_2":"Int64","FLAG_DOCUMENT_3":"Int64","FLAG_DOCUMENT_4":"Int64","FLAG_DOCUMENT_5":"Int64","FLAG_DOCUMENT_6":"Int64","FLAG_DOCUMENT_7":"Int64","FLAG_DOCUMENT_8":"Int64","FLAG_DOCUMENT_9":"Int64","FLAG_DOCUMENT_10":"Int64","FLAG_DOCUMENT_11":"Int64","FLAG_DOCUMENT_12":"Int64","FLAG_DOCUMENT_13":"Int64","FLAG_DOCUMENT_14":"Int64","FLAG_DOCUMENT_15":"Int64","FLAG_DOCUMENT_16":"Int64","FLAG_DOCUMENT_17":"Int64","FLAG_DOCUMENT_18":"Int64","FLAG_DOCUMENT_19":"Int64","FLAG_DOCUMENT_20":"Int64","FLAG_DOCUMENT_21":"Int64","AMT_REQ_CREDIT_BUREAU_HOUR":"Float64","AMT_REQ_CREDIT_BUREAU_DAY":"Float64","AMT_REQ_CREDIT_BUREAU_WEEK":"Float64","AMT_REQ_CREDIT_BUREAU_MON":"Float64","AMT_REQ_CREDIT_BUREAU_QRT":"Float64","AMT_REQ_CREDIT_BUREAU_YEAR":"Float64"},"metrics":["missing","zeros","mean","psi"],"group_col":"dataset_flag","time_col":null,"time_grain":null,"benchmark_row_count":215374,"categorical_features":["NAME_CONTRACT_TYPE","CODE_GENDER","FLAG_OWN_CAR","FLAG_OWN_REALTY","NAME_TYPE_SUITE","NAME_INCOME_TYPE","NAME_EDUCATION_TYPE","NAME_FAMILY_STATUS","NAME_HOUSING_TYPE","OCCUPATION_TYPE","WEEKDAY_APPR_PROCESS_START","ORGANIZATION_TYPE","FONDKAPREMONT_MODE","HOUSETYPE_MODE","WALLSMATERIAL_MODE","EMERGENCYSTATE_MODE"],"profile_config":{"missing_values":[],"special_values":[],"overview_batch_size":500,"psi_batch_size":50,"psi_remove_empty_bins":true,"psi_merge_small_bins":true,"psi_min_bin_size":0.02,"psi_cv_ignore_threshold":0.05,"enable_sparkline":false,"sparkline_sample_size":200000,"sparkline_bins":8,"psi_n_bins":10,"psi_bin_method":"quantile","psi_include_missing":false,"psi_include_special":false},"diagnostics":[]}</t>
+    <t>{"mars_version":"0.0.28","polars_version":"1.42.0","generated_at_utc":"2026-10-22T16:20:02.583139+00:00","input_type":"polars","row_count":356255,"column_count":124,"features":["NAME_CONTRACT_TYPE","CODE_GENDER","FLAG_OWN_CAR","FLAG_OWN_REALTY","CNT_CHILDREN","AMT_INCOME_TOTAL","AMT_ANNUITY","AMT_GOODS_PRICE","NAME_TYPE_SUITE","NAME_INCOME_TYPE","NAME_EDUCATION_TYPE","NAME_FAMILY_STATUS","NAME_HOUSING_TYPE","REGION_POPULATION_RELATIVE","DAYS_BIRTH","DAYS_EMPLOYED","DAYS_REGISTRATION","DAYS_ID_PUBLISH","OWN_CAR_AGE","FLAG_MOBIL","FLAG_EMP_PHONE","FLAG_WORK_PHONE","FLAG_CONT_MOBILE","FLAG_PHONE","FLAG_EMAIL","OCCUPATION_TYPE","CNT_FAM_MEMBERS","REGION_RATING_CLIENT","REGION_RATING_CLIENT_W_CITY","WEEKDAY_APPR_PROCESS_START","HOUR_APPR_PROCESS_START","REG_REGION_NOT_LIVE_REGION","REG_REGION_NOT_WORK_REGION","LIVE_REGION_NOT_WORK_REGION","REG_CITY_NOT_LIVE_CITY","REG_CITY_NOT_WORK_CITY","LIVE_CITY_NOT_WORK_CITY","ORGANIZATION_TYPE","EXT_SOURCE_1","EXT_SOURCE_2","EXT_SOURCE_3","APARTMENTS_AVG","BASEMENTAREA_AVG","YEARS_BEGINEXPLUATATION_AVG","YEARS_BUILD_AVG","COMMONAREA_AVG","ELEVATORS_AVG","ENTRANCES_AVG","FLOORSMAX_AVG","FLOORSMIN_AVG","LANDAREA_AVG","LIVINGAPARTMENTS_AVG","LIVINGAREA_AVG","NONLIVINGAPARTMENTS_AVG","NONLIVINGAREA_AVG","APARTMENTS_MODE","BASEMENTAREA_MODE","YEARS_BEGINEXPLUATATION_MODE","YEARS_BUILD_MODE","COMMONAREA_MODE","ELEVATORS_MODE","ENTRANCES_MODE","FLOORSMAX_MODE","FLOORSMIN_MODE","LANDAREA_MODE","LIVINGAPARTMENTS_MODE","LIVINGAREA_MODE","NONLIVINGAPARTMENTS_MODE","NONLIVINGAREA_MODE","APARTMENTS_MEDI","BASEMENTAREA_MEDI","YEARS_BEGINEXPLUATATION_MEDI","YEARS_BUILD_MEDI","COMMONAREA_MEDI","ELEVATORS_MEDI","ENTRANCES_MEDI","FLOORSMAX_MEDI","FLOORSMIN_MEDI","LANDAREA_MEDI","LIVINGAPARTMENTS_MEDI","LIVINGAREA_MEDI","NONLIVINGAPARTMENTS_MEDI","NONLIVINGAREA_MEDI","FONDKAPREMONT_MODE","HOUSETYPE_MODE","TOTALAREA_MODE","WALLSMATERIAL_MODE","EMERGENCYSTATE_MODE","OBS_30_CNT_SOCIAL_CIRCLE","DEF_30_CNT_SOCIAL_CIRCLE","OBS_60_CNT_SOCIAL_CIRCLE","DEF_60_CNT_SOCIAL_CIRCLE","DAYS_LAST_PHONE_CHANGE","FLAG_DOCUMENT_2","FLAG_DOCUMENT_3","FLAG_DOCUMENT_4","FLAG_DOCUMENT_5","FLAG_DOCUMENT_6","FLAG_DOCUMENT_7","FLAG_DOCUMENT_8","FLAG_DOCUMENT_9","FLAG_DOCUMENT_10","FLAG_DOCUMENT_11","FLAG_DOCUMENT_12","FLAG_DOCUMENT_13","FLAG_DOCUMENT_14","FLAG_DOCUMENT_15","FLAG_DOCUMENT_16","FLAG_DOCUMENT_17","FLAG_DOCUMENT_18","FLAG_DOCUMENT_19","FLAG_DOCUMENT_20","FLAG_DOCUMENT_21","AMT_REQ_CREDIT_BUREAU_HOUR","AMT_REQ_CREDIT_BUREAU_DAY","AMT_REQ_CREDIT_BUREAU_WEEK","AMT_REQ_CREDIT_BUREAU_MON","AMT_REQ_CREDIT_BUREAU_QRT","AMT_REQ_CREDIT_BUREAU_YEAR"],"feature_dtypes":{"NAME_CONTRACT_TYPE":"String","CODE_GENDER":"String","FLAG_OWN_CAR":"String","FLAG_OWN_REALTY":"String","CNT_CHILDREN":"Int64","AMT_INCOME_TOTAL":"Float64","AMT_ANNUITY":"Float64","AMT_GOODS_PRICE":"Float64","NAME_TYPE_SUITE":"String","NAME_INCOME_TYPE":"String","NAME_EDUCATION_TYPE":"String","NAME_FAMILY_STATUS":"String","NAME_HOUSING_TYPE":"String","REGION_POPULATION_RELATIVE":"Float64","DAYS_BIRTH":"Int64","DAYS_EMPLOYED":"Int64","DAYS_REGISTRATION":"Float64","DAYS_ID_PUBLISH":"Int64","OWN_CAR_AGE":"Float64","FLAG_MOBIL":"Int64","FLAG_EMP_PHONE":"Int64","FLAG_WORK_PHONE":"Int64","FLAG_CONT_MOBILE":"Int64","FLAG_PHONE":"Int64","FLAG_EMAIL":"Int64","OCCUPATION_TYPE":"String","CNT_FAM_MEMBERS":"Float64","REGION_RATING_CLIENT":"Int64","REGION_RATING_CLIENT_W_CITY":"Int64","WEEKDAY_APPR_PROCESS_START":"String","HOUR_APPR_PROCESS_START":"Int64","REG_REGION_NOT_LIVE_REGION":"Int64","REG_REGION_NOT_WORK_REGION":"Int64","LIVE_REGION_NOT_WORK_REGION":"Int64","REG_CITY_NOT_LIVE_CITY":"Int64","REG_CITY_NOT_WORK_CITY":"Int64","LIVE_CITY_NOT_WORK_CITY":"Int64","ORGANIZATION_TYPE":"String","EXT_SOURCE_1":"Float64","EXT_SOURCE_2":"Float64","EXT_SOURCE_3":"Float64","APARTMENTS_AVG":"Float64","BASEMENTAREA_AVG":"Float64","YEARS_BEGINEXPLUATATION_AVG":"Float64","YEARS_BUILD_AVG":"Float64","COMMONAREA_AVG":"Float64","ELEVATORS_AVG":"Float64","ENTRANCES_AVG":"Float64","FLOORSMAX_AVG":"Float64","FLOORSMIN_AVG":"Float64","LANDAREA_AVG":"Float64","LIVINGAPARTMENTS_AVG":"Float64","LIVINGAREA_AVG":"Float64","NONLIVINGAPARTMENTS_AVG":"Float64","NONLIVINGAREA_AVG":"Float64","APARTMENTS_MODE":"Float64","BASEMENTAREA_MODE":"Float64","YEARS_BEGINEXPLUATATION_MODE":"Float64","YEARS_BUILD_MODE":"Float64","COMMONAREA_MODE":"Float64","ELEVATORS_MODE":"Float64","ENTRANCES_MODE":"Float64","FLOORSMAX_MODE":"Float64","FLOORSMIN_MODE":"Float64","LANDAREA_MODE":"Float64","LIVINGAPARTMENTS_MODE":"Float64","LIVINGAREA_MODE":"Float64","NONLIVINGAPARTMENTS_MODE":"Float64","NONLIVINGAREA_MODE":"Float64","APARTMENTS_MEDI":"Float64","BASEMENTAREA_MEDI":"Float64","YEARS_BEGINEXPLUATATION_MEDI":"Float64","YEARS_BUILD_MEDI":"Float64","COMMONAREA_MEDI":"Float64","ELEVATORS_MEDI":"Float64","ENTRANCES_MEDI":"Float64","FLOORSMAX_MEDI":"Float64","FLOORSMIN_MEDI":"Float64","LANDAREA_MEDI":"Float64","LIVINGAPARTMENTS_MEDI":"Float64","LIVINGAREA_MEDI":"Float64","NONLIVINGAPARTMENTS_MEDI":"Float64","NONLIVINGAREA_MEDI":"Float64","FONDKAPREMONT_MODE":"String","HOUSETYPE_MODE":"String","TOTALAREA_MODE":"Float64","WALLSMATERIAL_MODE":"String","EMERGENCYSTATE_MODE":"String","OBS_30_CNT_SOCIAL_CIRCLE":"Float64","DEF_30_CNT_SOCIAL_CIRCLE":"Float64","OBS_60_CNT_SOCIAL_CIRCLE":"Float64","DEF_60_CNT_SOCIAL_CIRCLE":"Float64","DAYS_LAST_PHONE_CHANGE":"Float64","FLAG_DOCUMENT_2":"Int64","FLAG_DOCUMENT_3":"Int64","FLAG_DOCUMENT_4":"Int64","FLAG_DOCUMENT_5":"Int64","FLAG_DOCUMENT_6":"Int64","FLAG_DOCUMENT_7":"Int64","FLAG_DOCUMENT_8":"Int64","FLAG_DOCUMENT_9":"Int64","FLAG_DOCUMENT_10":"Int64","FLAG_DOCUMENT_11":"Int64","FLAG_DOCUMENT_12":"Int64","FLAG_DOCUMENT_13":"Int64","FLAG_DOCUMENT_14":"Int64","FLAG_DOCUMENT_15":"Int64","FLAG_DOCUMENT_16":"Int64","FLAG_DOCUMENT_17":"Int64","FLAG_DOCUMENT_18":"Int64","FLAG_DOCUMENT_19":"Int64","FLAG_DOCUMENT_20":"Int64","FLAG_DOCUMENT_21":"Int64","AMT_REQ_CREDIT_BUREAU_HOUR":"Float64","AMT_REQ_CREDIT_BUREAU_DAY":"Float64","AMT_REQ_CREDIT_BUREAU_WEEK":"Float64","AMT_REQ_CREDIT_BUREAU_MON":"Float64","AMT_REQ_CREDIT_BUREAU_QRT":"Float64","AMT_REQ_CREDIT_BUREAU_YEAR":"Float64"},"metrics":["missing","zeros","mean","psi"],"group_col":"dataset_flag","time_col":null,"time_grain":null,"benchmark_row_count":215374,"categorical_features":["NAME_CONTRACT_TYPE","CODE_GENDER","FLAG_OWN_CAR","FLAG_OWN_REALTY","NAME_TYPE_SUITE","NAME_INCOME_TYPE","NAME_EDUCATION_TYPE","NAME_FAMILY_STATUS","NAME_HOUSING_TYPE","OCCUPATION_TYPE","WEEKDAY_APPR_PROCESS_START","ORGANIZATION_TYPE","FONDKAPREMONT_MODE","HOUSETYPE_MODE","WALLSMATERIAL_MODE","EMERGENCYSTATE_MODE"],"profile_config":{"missing_values":[],"special_values":[],"overview_batch_size":500,"psi_batch_size":50,"psi_remove_empty_bins":true,"psi_merge_small_bins":true,"psi_min_bin_size":0.02,"psi_cv_ignore_threshold":0.05,"enable_sparkline":false,"sparkline_sample_size":200000,"sparkline_bins":8,"psi_n_bins":10,"psi_bin_method":"quantile","psi_include_missing":false,"psi_include_special":false},"diagnostics":[]}</t>
   </si>
   <si>
     <t>["只组织已有统计，未计算表不在目录中；失败和跳过见 parameters.diagnostics / fit_failures。","Null 不是数值 0；风险指标需结合标签表现状态，样本分布使用全样本。","比较前核对样本范围、权重、缺失/特殊箱、拟合来源、排序口径及参考来源；关联不代表因果。"]</t>
@@ -1237,7 +1237,7 @@
     <t>['NAME_CONTRACT_TYPE', 'CODE_GENDER', 'FLAG_OWN_CAR', 'FLAG_OWN_REALTY', 'CNT_CHILDREN', 'AMT_INCOME_TOTAL', 'AMT_ANNUITY', 'AMT_GOODS_PRICE', 'NAME_TYPE_SUITE', 'NAME_INCOME_TYPE', 'NAME_EDUCATION_TYPE', 'NAME_FAMILY_STATUS', 'NAME_HOUSING_TYPE', 'REGION_POPULATION_RELATIVE', 'DAYS_BIRTH', 'DAYS_EMPLOYED', 'DAYS_REGISTRATION', 'DAYS_ID_PUBLISH', 'OWN_CAR_AGE', 'FLAG_MOBIL', 'FLAG_EMP_PHONE', 'FLAG_WORK_PHONE', 'FLAG_CONT_MOBILE', 'FLAG_PHONE', 'FLAG_EMAIL', 'OCCUPATION_TYPE', 'CNT_FAM_MEMBERS', 'REGION_RATING_CLIENT', 'REGION_RATING_CLIENT_W_CITY', 'WEEKDAY_APPR_PROCESS_START', 'HOUR_APPR_PROCESS_START', 'REG_REGION_NOT_LIVE_REGION', 'REG_REGION_NOT_WORK_REGION', 'LIVE_REGION_NOT_WORK_REGION', 'REG_CITY_NOT_LIVE_CITY', 'REG_CITY_NOT_WORK_CITY', 'LIVE_CITY_NOT_WORK_CITY', 'ORGANIZATION_TYPE', 'EXT_SOURCE_1', 'EXT_SOURCE_2', 'EXT_SOURCE_3', 'APARTMENTS_AVG', 'BASEMENTAREA_AVG', 'YEARS_BEGINEXPLUATATION_AVG', 'YEARS_BUILD_AVG', 'COMMONAREA_AVG', 'ELEVATORS_AVG', 'ENTRANCES_AVG', 'FLOORSMAX_AVG', 'FLOORSMIN_AVG', 'LANDAREA_AVG', 'LIVINGAPARTMENTS_AVG', 'LIVINGAREA_AVG', 'NONLIVINGAPARTMENTS_AVG', 'NONLIVINGAREA_AVG', 'APARTMENTS_MODE', 'BASEMENTAREA_MODE', 'YEARS_BEGINEXPLUATATION_MODE', 'YEARS_BUILD_MODE', 'COMMONAREA_MODE', 'ELEVATORS_MODE', 'ENTRANCES_MODE', 'FLOORSMAX_MODE', 'FLOORSMIN_MODE', 'LANDAREA_MODE', 'LIVINGAPARTMENTS_MODE', 'LIVINGAREA_MODE', 'NONLIVINGAPARTMENTS_MODE', 'NONLIVINGAREA_MODE', 'APARTMENTS_MEDI', 'BASEMENTAREA_MEDI', 'YEARS_BEGINEXPLUATATION_MEDI', 'YEARS_BUILD_MEDI', 'COMMONAREA_MEDI', 'ELEVATORS_MEDI', 'ENTRANCES_MEDI', 'FLOORSMAX_MEDI', 'FLOORSMIN_MEDI', 'LANDAREA_MEDI', 'LIVINGAPARTMENTS_MEDI', 'LIVINGAREA_MEDI', 'NONLIVINGAPARTMENTS_MEDI', 'NONLIVINGAREA_MEDI', 'FONDKAPREMONT_MODE', 'HOUSETYPE_MODE', 'TOTALAREA_MODE', 'WALLSMATERIAL_MODE', 'EMERGENCYSTATE_MODE', 'OBS_30_CNT_SOCIAL_CIRCLE', 'DEF_30_CNT_SOCIAL_CIRCLE', 'OBS_60_CNT_SOCIAL_CIRCLE', 'DEF_60_CNT_SOCIAL_CIRCLE', 'DAYS_LAST_PHONE_CHANGE', 'FLAG_DOCUMENT_2', 'FLAG_DOCUMENT_3', 'FLAG_DOCUMENT_4', 'FLAG_DOCUMENT_5', 'FLAG_DOCUMENT_6', 'FLAG_DOCUMENT_7', 'FLAG_DOCUMENT_8', 'FLAG_DOCUMENT_9', 'FLAG_DOCUMENT_10', 'FLAG_DOCUMENT_11', 'FLAG_DOCUMENT_12', 'FLAG_DOCUMENT_13', 'FLAG_DOCUMENT_14', 'FLAG_DOCUMENT_15', 'FLAG_DOCUMENT_16', 'FLAG_DOCUMENT_17', 'FLAG_DOCUMENT_18', 'FLAG_DOCUMENT_19', 'FLAG_DOCUMENT_20', 'FLAG_DOCUMENT_21', 'AMT_REQ_CREDIT_BUREAU_HOUR', 'AMT_REQ_CREDIT_BUREAU_DAY', 'AMT_REQ_CREDIT_BUREAU_WEEK', 'AMT_REQ_CREDIT_BUREAU_MON', 'AMT_REQ_CREDIT_BUREAU_QRT', 'AMT_REQ_CREDIT_BUREAU_YEAR']</t>
   </si>
   <si>
-    <t>2026-10-22T15:04:08.748771+00:00</t>
+    <t>2026-10-22T16:20:02.583139+00:00</t>
   </si>
   <si>
     <t>dataset_flag</t>
@@ -5319,16 +5319,16 @@
         <v>0</v>
       </c>
       <c r="F6" s="146">
-        <v>0.000272674671959132</v>
+        <v>0.0002726746719591321</v>
       </c>
       <c r="G6" s="146">
         <v>0.0004359908872592861</v>
       </c>
       <c r="H6" s="146">
-        <v>0.0001317530575212157</v>
+        <v>0.0001317530575212158</v>
       </c>
       <c r="I6" s="153">
-        <v>0.07906116106137592</v>
+        <v>0.07906116106137594</v>
       </c>
       <c r="J6" s="146">
         <v>0.001365279438322753</v>
@@ -5351,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="146">
-        <v>0.0004229575247267528</v>
+        <v>0.0004229575247267527</v>
       </c>
       <c r="G7" s="146">
         <v>0.0004568298256773325</v>
@@ -5360,7 +5360,7 @@
         <v>0.0008412703074470193</v>
       </c>
       <c r="I7" s="154">
-        <v>0.06750590286014699</v>
+        <v>0.06750590286014697</v>
       </c>
       <c r="J7" s="146">
         <v>0.00128778006731055</v>
@@ -5383,7 +5383,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="146">
-        <v>0.0004114582672013995</v>
+        <v>0.0004114582672013996</v>
       </c>
       <c r="G8" s="146">
         <v>0.0001775186430226059</v>
@@ -5392,7 +5392,7 @@
         <v>0.0003406410569698186</v>
       </c>
       <c r="I8" s="154">
-        <v>0.06733499123360268</v>
+        <v>0.0673349912336027</v>
       </c>
       <c r="J8" s="146">
         <v>0.001132385811507225</v>
@@ -5418,16 +5418,16 @@
         <v>0.0006750568107998361</v>
       </c>
       <c r="G9" s="146">
-        <v>0.001165957983750372</v>
+        <v>0.001165957983750373</v>
       </c>
       <c r="H9" s="146">
-        <v>0.0007635089613454508</v>
+        <v>0.0007635089613454507</v>
       </c>
       <c r="I9" s="155">
-        <v>0.05393939544735973</v>
+        <v>0.05393939544735974</v>
       </c>
       <c r="J9" s="146">
-        <v>0.0009573998804793469</v>
+        <v>0.0009573998804793471</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -5450,16 +5450,16 @@
         <v>0.000523830081062208</v>
       </c>
       <c r="G10" s="146">
-        <v>0.0003435973883749282</v>
+        <v>0.0003435973883749283</v>
       </c>
       <c r="H10" s="146">
-        <v>0.0002656958730702188</v>
+        <v>0.0002656958730702189</v>
       </c>
       <c r="I10" s="156">
         <v>0.03332165477534482</v>
       </c>
       <c r="J10" s="146">
-        <v>0.000696270474266755</v>
+        <v>0.0006962704742667549</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="146">
-        <v>0.0002917040259570371</v>
+        <v>0.000291704025957037</v>
       </c>
       <c r="G13" s="146">
         <v>0.0003695330754674947</v>
@@ -5552,10 +5552,10 @@
         <v>0.0001648096561912276</v>
       </c>
       <c r="I13" s="159">
-        <v>0.02041594532379953</v>
+        <v>0.02041594532379954</v>
       </c>
       <c r="J13" s="146">
-        <v>0.000386653408720692</v>
+        <v>0.0003866534087206919</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -5578,7 +5578,7 @@
         <v>0.0003422263055754879</v>
       </c>
       <c r="G14" s="146">
-        <v>0.0005107138596507149</v>
+        <v>0.000510713859650715</v>
       </c>
       <c r="H14" s="146">
         <v>0.0003549349576677702</v>
@@ -5587,7 +5587,7 @@
         <v>0.01040017512456628</v>
       </c>
       <c r="J14" s="146">
-        <v>0.0002408577081781502</v>
+        <v>0.0002408577081781503</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -5613,7 +5613,7 @@
         <v>0.0005673208372032511</v>
       </c>
       <c r="H15" s="146">
-        <v>0.0008164301070808327</v>
+        <v>0.0008164301070808326</v>
       </c>
       <c r="I15" s="161">
         <v>0.004706356609441836</v>
@@ -5639,13 +5639,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="146">
-        <v>0.0009046902798901655</v>
+        <v>0.0009046902798901654</v>
       </c>
       <c r="G16" s="146">
         <v>0.0006650050198618814</v>
       </c>
       <c r="H16" s="146">
-        <v>0.0008138196494789251</v>
+        <v>0.0008138196494789252</v>
       </c>
       <c r="I16" s="161">
         <v>0.004697141218003738</v>
@@ -5703,16 +5703,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="146">
-        <v>0.001650933059097767</v>
+        <v>0.001650933059097768</v>
       </c>
       <c r="G18" s="146">
         <v>0.0008336962051746352</v>
       </c>
       <c r="H18" s="146">
-        <v>0.0007278830184852888</v>
+        <v>0.0007278830184852887</v>
       </c>
       <c r="I18" s="161">
-        <v>0.004137764121160776</v>
+        <v>0.004137764121160777</v>
       </c>
       <c r="J18" s="146">
         <v>0.000192604004751294</v>
@@ -5735,7 +5735,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="146">
-        <v>0.0004556121891369469</v>
+        <v>0.0004556121891369468</v>
       </c>
       <c r="G19" s="146">
         <v>0.0005330953972298455</v>
@@ -5802,13 +5802,13 @@
         <v>0.0005279165989653998</v>
       </c>
       <c r="G21" s="146">
-        <v>0.0002105766961911642</v>
+        <v>0.0002105766961911643</v>
       </c>
       <c r="H21" s="146">
         <v>0.0001166876448391015</v>
       </c>
       <c r="I21" s="148">
-        <v>0.00656310634109442</v>
+        <v>0.006563106341094419</v>
       </c>
       <c r="J21" s="146">
         <v>0.0001470230075732909</v>
@@ -5834,16 +5834,16 @@
         <v>0.0009006046387112046</v>
       </c>
       <c r="G22" s="146">
-        <v>0.0007769785026426631</v>
+        <v>0.000776978502642663</v>
       </c>
       <c r="H22" s="146">
-        <v>0.0006726731336210814</v>
+        <v>0.0006726731336210813</v>
       </c>
       <c r="I22" s="150">
-        <v>0.003330570546054685</v>
+        <v>0.003330570546054684</v>
       </c>
       <c r="J22" s="146">
-        <v>0.0001435186658435046</v>
+        <v>0.0001435186658435047</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -5869,7 +5869,7 @@
         <v>0.0007391243637027696</v>
       </c>
       <c r="H23" s="146">
-        <v>0.0006388049920837873</v>
+        <v>0.0006388049920837874</v>
       </c>
       <c r="I23" s="150">
         <v>0.003162697881529729</v>
@@ -5898,13 +5898,13 @@
         <v>0.001272906562277207</v>
       </c>
       <c r="G24" s="146">
-        <v>0.0008823029735659298</v>
+        <v>0.0008823029735659297</v>
       </c>
       <c r="H24" s="146">
-        <v>0.0006656919657747209</v>
+        <v>0.000665691965774721</v>
       </c>
       <c r="I24" s="150">
-        <v>0.002985011706108473</v>
+        <v>0.002985011706108472</v>
       </c>
       <c r="J24" s="146">
         <v>0.0001284087597390522</v>
@@ -5927,10 +5927,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="146">
-        <v>0.001361777816957065</v>
+        <v>0.001361777816957066</v>
       </c>
       <c r="G25" s="146">
-        <v>0.0005540000586823034</v>
+        <v>0.0005540000586823033</v>
       </c>
       <c r="H25" s="146">
         <v>0.0004075110544693656</v>
@@ -5962,10 +5962,10 @@
         <v>0.00165730371084646</v>
       </c>
       <c r="G26" s="146">
-        <v>0.0008880392126619236</v>
+        <v>0.0008880392126619239</v>
       </c>
       <c r="H26" s="146">
-        <v>0.0006326469041948433</v>
+        <v>0.0006326469041948434</v>
       </c>
       <c r="I26" s="150">
         <v>0.00323394875003497</v>
@@ -5991,7 +5991,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="146">
-        <v>0.0009633003282023779</v>
+        <v>0.000963300328202378</v>
       </c>
       <c r="G27" s="146">
         <v>0.0006349675527692761</v>
@@ -6029,7 +6029,7 @@
         <v>0.0008782617878327252</v>
       </c>
       <c r="H28" s="146">
-        <v>0.0007356732431974095</v>
+        <v>0.0007356732431974097</v>
       </c>
       <c r="I28" s="150">
         <v>0.003084644650046323</v>
@@ -6064,7 +6064,7 @@
         <v>0.0002394331653234997</v>
       </c>
       <c r="I29" s="148">
-        <v>0.006376492008095779</v>
+        <v>0.00637649200809578</v>
       </c>
       <c r="J29" s="146">
         <v>0.000108165771738073</v>
@@ -6119,7 +6119,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="146">
-        <v>0.0005089967561114183</v>
+        <v>0.0005089967561114184</v>
       </c>
       <c r="G31" s="146">
         <v>0.0003009977067106791</v>
@@ -6186,10 +6186,10 @@
         <v>0.0007512884389942388</v>
       </c>
       <c r="G33" s="146">
-        <v>0.0004671529086438922</v>
+        <v>0.0004671529086438923</v>
       </c>
       <c r="H33" s="146">
-        <v>0.0005392374509245959</v>
+        <v>0.0005392374509245958</v>
       </c>
       <c r="I33" s="146">
         <v>0.001928759584783809</v>
@@ -6282,7 +6282,7 @@
         <v>0.0004058559676021507</v>
       </c>
       <c r="G36" s="146">
-        <v>0.0003294849134768536</v>
+        <v>0.0003294849134768535</v>
       </c>
       <c r="H36" s="146">
         <v>0.000351402091655311</v>
@@ -6291,7 +6291,7 @@
         <v>0.003027728072991942</v>
       </c>
       <c r="J36" s="146">
-        <v>9.485598193598406E-05</v>
+        <v>9.485598193598407E-05</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="146">
-        <v>0.0008371590995017185</v>
+        <v>0.0008371590995017184</v>
       </c>
       <c r="G38" s="146">
         <v>0.0008933594509923097</v>
@@ -6381,13 +6381,13 @@
         <v>0.000898709661868989</v>
       </c>
       <c r="H39" s="146">
-        <v>0.0008045020086613746</v>
+        <v>0.0008045020086613745</v>
       </c>
       <c r="I39" s="150">
         <v>0.003399327545300172</v>
       </c>
       <c r="J39" s="146">
-        <v>8.468567100324797E-05</v>
+        <v>8.468567100324798E-05</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -6439,10 +6439,10 @@
         <v>0</v>
       </c>
       <c r="F41" s="146">
-        <v>0.0009875491174354983</v>
+        <v>0.0009875491174354981</v>
       </c>
       <c r="G41" s="146">
-        <v>0.0005831103459684677</v>
+        <v>0.0005831103459684678</v>
       </c>
       <c r="H41" s="146">
         <v>0.0006929788320388085</v>
@@ -6547,7 +6547,7 @@
         <v>0.00204539480717465</v>
       </c>
       <c r="J44" s="146">
-        <v>7.62057472037503E-05</v>
+        <v>7.620574720375031E-05</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -6570,10 +6570,10 @@
         <v>0.0004061210446586284</v>
       </c>
       <c r="G45" s="146">
-        <v>0.0006415378609272536</v>
+        <v>0.0006415378609272539</v>
       </c>
       <c r="H45" s="146">
-        <v>0.000453667036332729</v>
+        <v>0.0004536670363327289</v>
       </c>
       <c r="I45" s="146">
         <v>0.00182207547862773</v>
@@ -6599,10 +6599,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="146">
-        <v>0.0003859949364064137</v>
+        <v>0.0003859949364064136</v>
       </c>
       <c r="G46" s="146">
-        <v>0.0002773173745272085</v>
+        <v>0.0002773173745272086</v>
       </c>
       <c r="H46" s="146">
         <v>0.0008791763185465449</v>
@@ -6637,13 +6637,13 @@
         <v>0.0001502002697825659</v>
       </c>
       <c r="H47" s="146">
-        <v>0.00033910012237492</v>
+        <v>0.0003391001223749199</v>
       </c>
       <c r="I47" s="146">
         <v>0.001930994764990302</v>
       </c>
       <c r="J47" s="146">
-        <v>6.109682358509211E-05</v>
+        <v>6.109682358509209E-05</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -6669,7 +6669,7 @@
         <v>0.0003938379231976477</v>
       </c>
       <c r="H48" s="146">
-        <v>0.0007092755957732804</v>
+        <v>0.0007092755957732806</v>
       </c>
       <c r="I48" s="146">
         <v>0.001112067799557301</v>
@@ -6733,13 +6733,13 @@
         <v>0.0004116445508652776</v>
       </c>
       <c r="H50" s="146">
-        <v>0.0005960434964701329</v>
+        <v>0.000596043496470133</v>
       </c>
       <c r="I50" s="146">
         <v>0.001096291546580009</v>
       </c>
       <c r="J50" s="146">
-        <v>5.806490537682129E-05</v>
+        <v>5.806490537682128E-05</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -6762,7 +6762,7 @@
         <v>0.0009017410571161372</v>
       </c>
       <c r="G51" s="146">
-        <v>0.0007281361170196919</v>
+        <v>0.000728136117019692</v>
       </c>
       <c r="H51" s="146">
         <v>0.0007769784503198826</v>
@@ -6771,7 +6771,7 @@
         <v>0.003197524760845585</v>
       </c>
       <c r="J51" s="146">
-        <v>5.73310692801041E-05</v>
+        <v>5.733106928010408E-05</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -6791,7 +6791,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="146">
-        <v>5.162554495058317E-05</v>
+        <v>5.162554495058318E-05</v>
       </c>
       <c r="G52" s="146">
         <v>8.32757428619729E-05</v>
@@ -6826,7 +6826,7 @@
         <v>0.00146294832796287</v>
       </c>
       <c r="G53" s="146">
-        <v>0.0009279497017872704</v>
+        <v>0.0009279497017872705</v>
       </c>
       <c r="H53" s="146">
         <v>0.000934498532420981</v>
@@ -6835,7 +6835,7 @@
         <v>0.003777746740475534</v>
       </c>
       <c r="J53" s="146">
-        <v>5.393001840965037E-05</v>
+        <v>5.393001840965038E-05</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -6867,7 +6867,7 @@
         <v>0.003673183179908199</v>
       </c>
       <c r="J54" s="146">
-        <v>5.280395853889535E-05</v>
+        <v>5.280395853889536E-05</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -6896,7 +6896,7 @@
         <v>0.0003893733481318932</v>
       </c>
       <c r="I55" s="146">
-        <v>0.000625097704653319</v>
+        <v>0.0006250977046533189</v>
       </c>
       <c r="J55" s="146">
         <v>5.189494514006359E-05</v>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="146">
-        <v>0.000554309432308755</v>
+        <v>0.0005543094323087549</v>
       </c>
       <c r="G56" s="146">
         <v>0.0006873867122607394</v>
@@ -6931,7 +6931,7 @@
         <v>0.000758801676910085</v>
       </c>
       <c r="J56" s="146">
-        <v>5.180834988266439E-05</v>
+        <v>5.180834988266437E-05</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -6951,10 +6951,10 @@
         <v>0</v>
       </c>
       <c r="F57" s="146">
-        <v>0.0007974564453622557</v>
+        <v>0.0007974564453622556</v>
       </c>
       <c r="G57" s="146">
-        <v>7.34004058676577E-05</v>
+        <v>7.340040586765771E-05</v>
       </c>
       <c r="H57" s="146">
         <v>0.0001350336952345964</v>
@@ -6995,7 +6995,7 @@
         <v>0.001586452647616574</v>
       </c>
       <c r="J58" s="146">
-        <v>5.088130811436231E-05</v>
+        <v>5.08813081143623E-05</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="146">
-        <v>0.0002069888926426198</v>
+        <v>0.0002069888926426199</v>
       </c>
       <c r="G59" s="146">
         <v>0.0001608385656067654</v>
@@ -7047,13 +7047,13 @@
         <v>0</v>
       </c>
       <c r="F60" s="146">
-        <v>0.00179448727627808</v>
+        <v>0.001794487276278081</v>
       </c>
       <c r="G60" s="146">
-        <v>0.001149722071685593</v>
+        <v>0.001149722071685594</v>
       </c>
       <c r="H60" s="146">
-        <v>0.000740224137337557</v>
+        <v>0.0007402241373375571</v>
       </c>
       <c r="I60" s="150">
         <v>0.003761064181919265</v>
@@ -7082,7 +7082,7 @@
         <v>0.0003436206978730976</v>
       </c>
       <c r="G61" s="146">
-        <v>0.0003558285538621642</v>
+        <v>0.0003558285538621641</v>
       </c>
       <c r="H61" s="146">
         <v>0.0002181422707407589</v>
@@ -7114,7 +7114,7 @@
         <v>0.0001388867730216045</v>
       </c>
       <c r="G62" s="146">
-        <v>0.000436160314042775</v>
+        <v>0.0004361603140427749</v>
       </c>
       <c r="H62" s="146">
         <v>0.0002174930525808354</v>
@@ -7123,7 +7123,7 @@
         <v>0.001138361207949628</v>
       </c>
       <c r="J62" s="146">
-        <v>4.508026381268987E-05</v>
+        <v>4.508026381268986E-05</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -7184,7 +7184,7 @@
         <v>0.0003377505929368465</v>
       </c>
       <c r="I64" s="146">
-        <v>0.0005056002511582028</v>
+        <v>0.0005056002511582029</v>
       </c>
       <c r="J64" s="146">
         <v>4.189222354836606E-05</v>
@@ -7248,7 +7248,7 @@
         <v>0.0001735836196081921</v>
       </c>
       <c r="I66" s="146">
-        <v>0.001841422951134757</v>
+        <v>0.001841422951134758</v>
       </c>
       <c r="J66" s="146">
         <v>3.634196110493259E-05</v>
@@ -7274,7 +7274,7 @@
         <v>0.0001203327264306773</v>
       </c>
       <c r="G67" s="146">
-        <v>0.0006928895512978085</v>
+        <v>0.0006928895512978086</v>
       </c>
       <c r="H67" s="146">
         <v>0.0001965028563277855</v>
@@ -7306,13 +7306,13 @@
         <v>0.0007461572027814187</v>
       </c>
       <c r="G68" s="146">
-        <v>0.0006544961187338143</v>
+        <v>0.0006544961187338145</v>
       </c>
       <c r="H68" s="146">
         <v>0.000350644640923031</v>
       </c>
       <c r="I68" s="146">
-        <v>0.0009029031762900729</v>
+        <v>0.000902903176290073</v>
       </c>
       <c r="J68" s="146">
         <v>3.512182112597062E-05</v>
@@ -7367,13 +7367,13 @@
         <v>0</v>
       </c>
       <c r="F70" s="146">
-        <v>0.0002089849590203702</v>
+        <v>0.0002089849590203701</v>
       </c>
       <c r="G70" s="146">
-        <v>0.0005458892885549272</v>
+        <v>0.0005458892885549271</v>
       </c>
       <c r="H70" s="146">
-        <v>0.0002777976510313733</v>
+        <v>0.0002777976510313732</v>
       </c>
       <c r="I70" s="150">
         <v>0.002045740586928956</v>
@@ -7399,7 +7399,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="146">
-        <v>0.000307833639063314</v>
+        <v>0.0003078336390633141</v>
       </c>
       <c r="G71" s="146">
         <v>0.0004032891911680437</v>
@@ -7463,7 +7463,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="146">
-        <v>4.922337563813201E-05</v>
+        <v>4.9223375638132E-05</v>
       </c>
       <c r="G73" s="146">
         <v>0.0003075762294441428</v>
@@ -7559,16 +7559,16 @@
         <v>0</v>
       </c>
       <c r="F76" s="146">
-        <v>0.0004761382144854723</v>
+        <v>0.0004761382144854724</v>
       </c>
       <c r="G76" s="146">
-        <v>0.0006350778082566487</v>
+        <v>0.0006350778082566488</v>
       </c>
       <c r="H76" s="146">
-        <v>0.0005807056819354495</v>
+        <v>0.0005807056819354496</v>
       </c>
       <c r="I76" s="146">
-        <v>0.0007993558356615605</v>
+        <v>0.0007993558356615606</v>
       </c>
       <c r="J76" s="146">
         <v>2.204468229393618E-05</v>
@@ -7655,16 +7655,16 @@
         <v>0</v>
       </c>
       <c r="F79" s="146">
-        <v>0.0005781458001414297</v>
+        <v>0.0005781458001414296</v>
       </c>
       <c r="G79" s="146">
-        <v>0.0001843307801176307</v>
+        <v>0.0001843307801176306</v>
       </c>
       <c r="H79" s="146">
         <v>2.736757282872682E-05</v>
       </c>
       <c r="I79" s="146">
-        <v>0.0008294003371478877</v>
+        <v>0.0008294003371478876</v>
       </c>
       <c r="J79" s="146">
         <v>1.957414016171001E-05</v>
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="F82" s="146">
-        <v>0.0001869037488759298</v>
+        <v>0.0001869037488759297</v>
       </c>
       <c r="G82" s="146">
         <v>0.000189896662860589</v>
@@ -7760,7 +7760,7 @@
         <v>0.0001618477010389814</v>
       </c>
       <c r="I82" s="146">
-        <v>0.0004078200660551567</v>
+        <v>0.0004078200660551566</v>
       </c>
       <c r="J82" s="146">
         <v>1.27616955569555E-05</v>
@@ -7783,16 +7783,16 @@
         <v>0</v>
       </c>
       <c r="F83" s="146">
-        <v>0.0003858378504215861</v>
+        <v>0.0003858378504215862</v>
       </c>
       <c r="G83" s="146">
         <v>0.0001433687264076162</v>
       </c>
       <c r="H83" s="146">
-        <v>0.0003501664781923937</v>
+        <v>0.0003501664781923938</v>
       </c>
       <c r="I83" s="146">
-        <v>0.0003739191734389024</v>
+        <v>0.0003739191734389025</v>
       </c>
       <c r="J83" s="146">
         <v>9.803484471619088E-06</v>
@@ -7923,7 +7923,7 @@
         <v>4.410448904972118E-05</v>
       </c>
       <c r="J87" s="146">
-        <v>4.50903366754307E-06</v>
+        <v>4.509033667543071E-06</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -7943,16 +7943,16 @@
         <v>0</v>
       </c>
       <c r="F88" s="146">
-        <v>0.0001030651974179945</v>
+        <v>0.0001030651974179946</v>
       </c>
       <c r="G88" s="146">
-        <v>0.0002225085141382576</v>
+        <v>0.0002225085141382575</v>
       </c>
       <c r="H88" s="146">
         <v>0.0001580613216774258</v>
       </c>
       <c r="I88" s="146">
-        <v>2.613720564824345E-05</v>
+        <v>2.613720564824346E-05</v>
       </c>
       <c r="J88" s="146">
         <v>3.743291536592727E-06</v>
@@ -8051,7 +8051,7 @@
         <v>2.21307750752358E-05</v>
       </c>
       <c r="J91" s="146">
-        <v>2.249837727138262E-06</v>
+        <v>2.249837727138263E-06</v>
       </c>
     </row>
     <row r="92" spans="1:10">
